--- a/hmm_regime_results.xlsx
+++ b/hmm_regime_results.xlsx
@@ -491,7 +491,7 @@
         <v>-2.915567756089579</v>
       </c>
       <c r="F2" t="n">
-        <v>7.948783884085062</v>
+        <v>7.94878388408506</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5231463948411231</v>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.948783884085062</v>
+        <v>7.94878388408506</v>
       </c>
       <c r="C10" t="n">
         <v>5.037871764325111</v>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8912042514088995</v>
+        <v>0.8912042514089229</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002610309312697777</v>
+        <v>0.002610309312686259</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1061854392784027</v>
+        <v>0.1061854392783908</v>
       </c>
     </row>
     <row r="23">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01677267542874276</v>
+        <v>0.01677267542875545</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9399474759227537</v>
+        <v>0.9399474759227125</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04327984864850351</v>
+        <v>0.04327984864853202</v>
       </c>
     </row>
     <row r="24">
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.073778591041221e-07</v>
+        <v>4.073778591080794e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04945640621365061</v>
+        <v>0.04945640621365294</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9505431864084902</v>
+        <v>0.9505431864084879</v>
       </c>
     </row>
     <row r="27">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8912042514088995</v>
+        <v>0.8912042514089229</v>
       </c>
       <c r="C28" t="n">
-        <v>9.19153563397421</v>
+        <v>9.191535633976189</v>
       </c>
     </row>
     <row r="29">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9399474759227537</v>
+        <v>0.9399474759227125</v>
       </c>
       <c r="C29" t="n">
-        <v>16.65208940616198</v>
+        <v>16.65208940615056</v>
       </c>
     </row>
     <row r="30">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9505431864084902</v>
+        <v>0.9505431864084879</v>
       </c>
       <c r="C30" t="n">
-        <v>20.21966089969997</v>
+        <v>20.21966089969901</v>
       </c>
     </row>
     <row r="33">
@@ -1163,7 +1163,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>1450.608958050785</v>
+        <v>1450.608958050789</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -1190,7 +1190,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="n">
-        <v>1449.465211539835</v>
+        <v>1449.465211539834</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>1449.464865138084</v>
+        <v>1449.46486513808</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -1271,7 +1271,7 @@
         <v>34</v>
       </c>
       <c r="B6" t="n">
-        <v>1447.669294036742</v>
+        <v>1447.66929403675</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1298,7 +1298,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>1445.230856115715</v>
+        <v>1445.230856115709</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -1325,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>1445.158382950025</v>
+        <v>1445.158382950023</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -1352,7 +1352,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>1444.973366121271</v>
+        <v>1444.973366121276</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -1379,7 +1379,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>1444.91722057355</v>
+        <v>1444.917220573547</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -1406,7 +1406,7 @@
         <v>21</v>
       </c>
       <c r="B11" t="n">
-        <v>1444.525487836745</v>
+        <v>1444.525487836748</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -1433,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>1444.406453072128</v>
+        <v>1444.406453072126</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -1487,7 +1487,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>1444.352512517937</v>
+        <v>1444.352512517934</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
@@ -1514,7 +1514,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>1444.103822816122</v>
+        <v>1444.103822816126</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1541,7 +1541,7 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1443.773665341949</v>
+        <v>1443.773665341937</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1568,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="B17" t="n">
-        <v>1443.011302886119</v>
+        <v>1443.011302886111</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -1595,7 +1595,7 @@
         <v>32</v>
       </c>
       <c r="B18" t="n">
-        <v>1442.847806675568</v>
+        <v>1442.847806675563</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
@@ -1649,7 +1649,7 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1442.329755651854</v>
+        <v>1442.329755651856</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -1676,7 +1676,7 @@
         <v>36</v>
       </c>
       <c r="B21" t="n">
-        <v>1442.315405294311</v>
+        <v>1442.315405294313</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -1703,7 +1703,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="n">
-        <v>1442.289859040268</v>
+        <v>1442.28985904027</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -1730,7 +1730,7 @@
         <v>31</v>
       </c>
       <c r="B23" t="n">
-        <v>1442.264509661014</v>
+        <v>1442.264509661016</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -1757,7 +1757,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>1442.149762043644</v>
+        <v>1442.149762043645</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1811,7 +1811,7 @@
         <v>20</v>
       </c>
       <c r="B26" t="n">
-        <v>1441.208871552892</v>
+        <v>1441.208871552887</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
@@ -1838,7 +1838,7 @@
         <v>17</v>
       </c>
       <c r="B27" t="n">
-        <v>1441.018977467089</v>
+        <v>1441.018977467086</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
@@ -1865,7 +1865,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>1438.460111366149</v>
+        <v>1438.460111366152</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -1892,7 +1892,7 @@
         <v>18</v>
       </c>
       <c r="B29" t="n">
-        <v>1437.117579684988</v>
+        <v>1437.117579684986</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
@@ -1919,7 +1919,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="n">
-        <v>1437.01739033401</v>
+        <v>1437.017390334011</v>
       </c>
       <c r="C30" t="n">
         <v>3</v>
@@ -1946,7 +1946,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="n">
-        <v>1436.120410190309</v>
+        <v>1436.120410190316</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -1973,7 +1973,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n">
-        <v>1435.325754901706</v>
+        <v>1435.325754901698</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
@@ -2000,7 +2000,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="n">
-        <v>1433.61753672232</v>
+        <v>1433.617536722323</v>
       </c>
       <c r="C33" t="n">
         <v>3</v>
@@ -2054,7 +2054,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n">
-        <v>1432.907811009195</v>
+        <v>1432.907811009202</v>
       </c>
       <c r="C35" t="n">
         <v>3</v>
@@ -2081,7 +2081,7 @@
         <v>23</v>
       </c>
       <c r="B36" t="n">
-        <v>1432.432032674332</v>
+        <v>1432.432032674325</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
@@ -2108,7 +2108,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="n">
-        <v>1425.624908371039</v>
+        <v>1425.624908371038</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
@@ -2135,7 +2135,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>1423.879819855439</v>
+        <v>1423.879819855441</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
@@ -2290,7 +2290,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2.695728742195409e-180</v>
+        <v>2.695728742212571e-180</v>
       </c>
       <c r="F2" t="n">
         <v>2.963763009676205e-64</v>
@@ -2307,16 +2307,16 @@
         <v>0.03746962579352606</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008686003136073352</v>
+        <v>0.0008686003136073347</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.814186709792344e-08</v>
+        <v>2.814186709819219e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003353761425795718</v>
+        <v>0.003353761425796481</v>
       </c>
       <c r="G3" t="n">
         <v>0.9966462104322613</v>
@@ -2336,10 +2336,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001502987859032939</v>
+        <v>0.0001502987859033964</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004863281705301384</v>
+        <v>0.004863281705300279</v>
       </c>
       <c r="G4" t="n">
         <v>0.9949864195088571</v>
@@ -2359,7 +2359,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3.041605998305264e-05</v>
+        <v>3.041605998306647e-05</v>
       </c>
       <c r="F5" t="n">
         <v>0.01995345186181575</v>
@@ -2382,10 +2382,10 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2.642319424216312e-05</v>
+        <v>2.642319424217514e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04370309379134062</v>
+        <v>0.04370309379133067</v>
       </c>
       <c r="G6" t="n">
         <v>0.9562704830143549</v>
@@ -2405,10 +2405,10 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>8.222449623344992e-05</v>
+        <v>8.222449623350601e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08402246932893309</v>
+        <v>0.08402246932891398</v>
       </c>
       <c r="G7" t="n">
         <v>0.9158953061748766</v>
@@ -2428,10 +2428,10 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>6.223769141748313e-05</v>
+        <v>6.223769141749728e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1805652995290413</v>
+        <v>0.1805652995289591</v>
       </c>
       <c r="G8" t="n">
         <v>0.8193724627795731</v>
@@ -2451,10 +2451,10 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001481863854175362</v>
+        <v>0.0001481863854176036</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2810602805884828</v>
+        <v>0.2810602805884189</v>
       </c>
       <c r="G9" t="n">
         <v>0.7187915330261294</v>
@@ -2474,10 +2474,10 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001173969052949258</v>
+        <v>0.0001173969052949792</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3596262203603621</v>
+        <v>0.3596262203602803</v>
       </c>
       <c r="G10" t="n">
         <v>0.6402563827343656</v>
@@ -2497,10 +2497,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001936363167384203</v>
+        <v>0.0001936363167385524</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5019955359896534</v>
+        <v>0.5019955359895393</v>
       </c>
       <c r="G11" t="n">
         <v>0.4978108276937149</v>
@@ -2520,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0002336311773313874</v>
+        <v>0.0002336311773315468</v>
       </c>
       <c r="F12" t="n">
         <v>0.5559426619097101</v>
@@ -2543,10 +2543,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0002384769645240335</v>
+        <v>0.0002384769645240877</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6009905273642874</v>
+        <v>0.6009905273641507</v>
       </c>
       <c r="G13" t="n">
         <v>0.3987709956712986</v>
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0006181490396130483</v>
+        <v>0.00061814903961347</v>
       </c>
       <c r="F14" t="n">
         <v>0.7162527429304237</v>
@@ -2589,13 +2589,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00188796460441712</v>
+        <v>0.001887964604417549</v>
       </c>
       <c r="F15" t="n">
         <v>0.8059798729508935</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1921321624447326</v>
+        <v>0.1921321624446015</v>
       </c>
     </row>
     <row r="16">
@@ -2612,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002230375988287132</v>
+        <v>0.002230375988288147</v>
       </c>
       <c r="F16" t="n">
         <v>0.8317411251949975</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1660284988167111</v>
+        <v>0.1660284988166733</v>
       </c>
     </row>
     <row r="17">
@@ -2635,13 +2635,13 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004413137124634325</v>
+        <v>0.004413137124637334</v>
       </c>
       <c r="F17" t="n">
         <v>0.8395405693993977</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1560462934759389</v>
+        <v>0.1560462934759744</v>
       </c>
     </row>
     <row r="18">
@@ -2658,10 +2658,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002632773941092465</v>
+        <v>0.002632773941093063</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8445756927244211</v>
+        <v>0.8445756927242292</v>
       </c>
       <c r="G18" t="n">
         <v>0.1527915333345857</v>
@@ -2681,13 +2681,13 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001088341438560127</v>
+        <v>0.001088341438560621</v>
       </c>
       <c r="F19" t="n">
         <v>0.8549369009706812</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1439747575907272</v>
+        <v>0.1439747575907599</v>
       </c>
     </row>
     <row r="20">
@@ -2704,13 +2704,13 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0003246533925774246</v>
+        <v>0.0003246533925774983</v>
       </c>
       <c r="F20" t="n">
         <v>0.8645564831649317</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1351188634424592</v>
+        <v>0.1351188634424899</v>
       </c>
     </row>
     <row r="21">
@@ -2721,19 +2721,19 @@
         <v>-0.02054671670874412</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002590752718941235</v>
+        <v>0.002590752718941236</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0001864477730100626</v>
+        <v>0.0001864477730099354</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8990503017291671</v>
+        <v>0.8990503017289627</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1007632504978934</v>
+        <v>0.1007632504979393</v>
       </c>
     </row>
     <row r="22">
@@ -2750,13 +2750,13 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0001584670171042186</v>
+        <v>0.0001584670171040385</v>
       </c>
       <c r="F22" t="n">
         <v>0.9311195581613873</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06872197482152588</v>
+        <v>0.06872197482154151</v>
       </c>
     </row>
     <row r="23">
@@ -2773,13 +2773,13 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0002743312298666671</v>
+        <v>0.00027433122986648</v>
       </c>
       <c r="F23" t="n">
         <v>0.9844874874686476</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01523818130151862</v>
+        <v>0.01523818130152208</v>
       </c>
     </row>
     <row r="24">
@@ -2787,22 +2787,22 @@
         <v>36830</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.009817373019298678</v>
+        <v>-0.00981737301929868</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0035647155073691</v>
+        <v>0.003564715507369099</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0001816467165632608</v>
+        <v>0.0001816467165631782</v>
       </c>
       <c r="F24" t="n">
         <v>0.9885314406964752</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01128691258699371</v>
+        <v>0.0112869125870014</v>
       </c>
     </row>
     <row r="25">
@@ -2842,13 +2842,13 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0002192768022868895</v>
+        <v>0.0002192768022867898</v>
       </c>
       <c r="F26" t="n">
         <v>0.9927865237920164</v>
       </c>
       <c r="G26" t="n">
-        <v>0.006994199405793355</v>
+        <v>0.006994199405798126</v>
       </c>
     </row>
     <row r="27">
@@ -2865,13 +2865,13 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0001754543377822731</v>
+        <v>0.0001754543377821135</v>
       </c>
       <c r="F27" t="n">
         <v>0.9906633294851697</v>
       </c>
       <c r="G27" t="n">
-        <v>0.009161216176934559</v>
+        <v>0.009161216176940807</v>
       </c>
     </row>
     <row r="28">
@@ -2888,13 +2888,13 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0004988365047885633</v>
+        <v>0.0004988365047883365</v>
       </c>
       <c r="F28" t="n">
         <v>0.999488798793971</v>
       </c>
       <c r="G28" t="n">
-        <v>1.236470128129709e-05</v>
+        <v>1.236470128130271e-05</v>
       </c>
     </row>
     <row r="29">
@@ -2911,13 +2911,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0006822719880416356</v>
+        <v>0.0006822719880417908</v>
       </c>
       <c r="F29" t="n">
         <v>0.9990766311342009</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0002410968776462157</v>
+        <v>0.0002410968776463253</v>
       </c>
     </row>
     <row r="30">
@@ -2934,13 +2934,13 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0005887989282695115</v>
+        <v>0.0005887989282697792</v>
       </c>
       <c r="F30" t="n">
         <v>0.9965508344781396</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002860366593687201</v>
+        <v>0.002860366593689803</v>
       </c>
     </row>
     <row r="31">
@@ -2948,7 +2948,7 @@
         <v>37042</v>
       </c>
       <c r="B31" t="n">
-        <v>0.003486086443238612</v>
+        <v>0.003486086443238613</v>
       </c>
       <c r="C31" t="n">
         <v>-0.001127279284296733</v>
@@ -2957,13 +2957,13 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0001436756635694483</v>
+        <v>0.0001436756635693502</v>
       </c>
       <c r="F31" t="n">
         <v>0.9885491525126985</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01130717182370655</v>
+        <v>0.01130717182371426</v>
       </c>
     </row>
     <row r="32">
@@ -2980,13 +2980,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0001200645665516225</v>
+        <v>0.0001200645665515133</v>
       </c>
       <c r="F32" t="n">
         <v>0.9919445288946664</v>
       </c>
       <c r="G32" t="n">
-        <v>0.007935406538828009</v>
+        <v>0.007935406538835225</v>
       </c>
     </row>
     <row r="33">
@@ -3003,13 +3003,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0001761582245676216</v>
+        <v>0.0001761582245675014</v>
       </c>
       <c r="F33" t="n">
         <v>0.9963622450527434</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003461596722648289</v>
+        <v>0.003461596722649863</v>
       </c>
     </row>
     <row r="34">
@@ -3020,7 +3020,7 @@
         <v>-0.06774638797380172</v>
       </c>
       <c r="C34" t="n">
-        <v>0.009266260116781109</v>
+        <v>0.009266260116781111</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -3032,7 +3032,7 @@
         <v>0.9994593969322402</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0001531433284863249</v>
+        <v>0.0001531433284864294</v>
       </c>
     </row>
     <row r="35">
@@ -3095,13 +3095,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001150385785360297</v>
+        <v>0.001150385785361081</v>
       </c>
       <c r="F37" t="n">
         <v>0.990423362328498</v>
       </c>
       <c r="G37" t="n">
-        <v>0.008426251886036677</v>
+        <v>0.008426251886040509</v>
       </c>
     </row>
     <row r="38">
@@ -3124,7 +3124,7 @@
         <v>0.9714970021387823</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02814353907290571</v>
+        <v>0.02814353907292491</v>
       </c>
     </row>
     <row r="39">
@@ -3135,19 +3135,19 @@
         <v>-0.01610219756674967</v>
       </c>
       <c r="C39" t="n">
-        <v>0.004747939606516225</v>
+        <v>0.004747939606516224</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001700794937549734</v>
+        <v>0.000170079493754896</v>
       </c>
       <c r="F39" t="n">
         <v>0.9749505810653646</v>
       </c>
       <c r="G39" t="n">
-        <v>0.02487933944098164</v>
+        <v>0.02487933944099296</v>
       </c>
     </row>
     <row r="40">
@@ -3158,19 +3158,19 @@
         <v>-0.02076850133664727</v>
       </c>
       <c r="C40" t="n">
-        <v>0.009776868601837064</v>
+        <v>0.009776868601837062</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0001441486729452173</v>
+        <v>0.0001441486729450862</v>
       </c>
       <c r="F40" t="n">
         <v>0.9818026854709171</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01805316585621692</v>
+        <v>0.01805316585622924</v>
       </c>
     </row>
     <row r="41">
@@ -3187,13 +3187,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.000169146932997933</v>
+        <v>0.0001691469329975869</v>
       </c>
       <c r="F41" t="n">
         <v>0.9860068330864624</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01382401998060598</v>
+        <v>0.01382401998061855</v>
       </c>
     </row>
     <row r="42">
@@ -3210,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0001911717908810368</v>
+        <v>0.0001911717908808629</v>
       </c>
       <c r="F42" t="n">
         <v>0.9995641905351547</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0002446376739435047</v>
+        <v>0.0002446376739436716</v>
       </c>
     </row>
     <row r="43">
@@ -3233,13 +3233,13 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>9.295858556853764e-05</v>
+        <v>9.295858556836855e-05</v>
       </c>
       <c r="F43" t="n">
         <v>0.9972168214437576</v>
       </c>
       <c r="G43" t="n">
-        <v>0.002690219970731196</v>
+        <v>0.002690219970733643</v>
       </c>
     </row>
     <row r="44">
@@ -3256,13 +3256,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001899892356814047</v>
+        <v>0.0001899892356812319</v>
       </c>
       <c r="F44" t="n">
         <v>0.9997799776169817</v>
       </c>
       <c r="G44" t="n">
-        <v>3.003314736041729e-05</v>
+        <v>3.003314736042412e-05</v>
       </c>
     </row>
     <row r="45">
@@ -3285,7 +3285,7 @@
         <v>0.9996355074685692</v>
       </c>
       <c r="G45" t="n">
-        <v>3.820908484399953e-06</v>
+        <v>3.820908484402559e-06</v>
       </c>
     </row>
     <row r="46">
@@ -3308,7 +3308,7 @@
         <v>0.996940271181159</v>
       </c>
       <c r="G46" t="n">
-        <v>0.002588167555721446</v>
+        <v>0.002588167555724388</v>
       </c>
     </row>
     <row r="47">
@@ -3331,7 +3331,7 @@
         <v>0.9989568387244523</v>
       </c>
       <c r="G47" t="n">
-        <v>1.393201608955034e-08</v>
+        <v>1.39320160895535e-08</v>
       </c>
     </row>
     <row r="48">
@@ -3348,13 +3348,13 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001594514387050777</v>
+        <v>0.001594514387051502</v>
       </c>
       <c r="F48" t="n">
         <v>0.9978258967269635</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0005795888860354011</v>
+        <v>0.0005795888860357965</v>
       </c>
     </row>
     <row r="49">
@@ -3371,13 +3371,13 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.003056709080027081</v>
+        <v>0.003056709080028471</v>
       </c>
       <c r="F49" t="n">
         <v>0.9948569332166738</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00208635770329389</v>
+        <v>0.002086357703294839</v>
       </c>
     </row>
     <row r="50">
@@ -3400,7 +3400,7 @@
         <v>0.9920961114771004</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0009691295518614085</v>
+        <v>0.0009691295518611881</v>
       </c>
     </row>
     <row r="51">
@@ -3417,10 +3417,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.008011043348989215</v>
+        <v>0.008011043348991036</v>
       </c>
       <c r="F51" t="n">
-        <v>0.893641339422794</v>
+        <v>0.8936413394225908</v>
       </c>
       <c r="G51" t="n">
         <v>0.09834761722830951</v>
@@ -3440,13 +3440,13 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.009587964923515217</v>
+        <v>0.009587964923519576</v>
       </c>
       <c r="F52" t="n">
         <v>0.8106483724595758</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1797636626168876</v>
+        <v>0.1797636626169284</v>
       </c>
     </row>
     <row r="53">
@@ -3466,10 +3466,10 @@
         <v>0.01145833573988345</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6232158107346395</v>
+        <v>0.6232158107344978</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3653258535255904</v>
+        <v>0.3653258535255073</v>
       </c>
     </row>
     <row r="54">
@@ -3486,13 +3486,13 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02828394809025208</v>
+        <v>0.02828394809026494</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5259809090704926</v>
+        <v>0.525980909070373</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4457351428392623</v>
+        <v>0.445735142839465</v>
       </c>
     </row>
     <row r="55">
@@ -3512,7 +3512,7 @@
         <v>0.05675565498017482</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2815879950287687</v>
+        <v>0.2815879950286407</v>
       </c>
       <c r="G55" t="n">
         <v>0.6616563499911349</v>
@@ -3532,10 +3532,10 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.05316550339534441</v>
+        <v>0.05316550339532024</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1901470355634048</v>
+        <v>0.1901470355633184</v>
       </c>
       <c r="G56" t="n">
         <v>0.7566874610413634</v>
@@ -3558,10 +3558,10 @@
         <v>0.08155353898760193</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1280151798828483</v>
+        <v>0.128015179882761</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7904312811294965</v>
+        <v>0.7904312811296762</v>
       </c>
     </row>
     <row r="58">
@@ -3581,7 +3581,7 @@
         <v>0.03946510860119001</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1373463346019925</v>
+        <v>0.13734633460193</v>
       </c>
       <c r="G58" t="n">
         <v>0.8231885567968273</v>
@@ -3601,7 +3601,7 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0.03517522672853798</v>
+        <v>0.03517522672854598</v>
       </c>
       <c r="F59" t="n">
         <v>0.167417159191378</v>
@@ -3647,10 +3647,10 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003149267453557575</v>
+        <v>0.003149267453558291</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09087015719980107</v>
+        <v>0.09087015719978041</v>
       </c>
       <c r="G61" t="n">
         <v>0.9059805753466813</v>
@@ -3670,10 +3670,10 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.001147264716336135</v>
+        <v>0.001147264716336656</v>
       </c>
       <c r="F62" t="n">
-        <v>0.06493899762013398</v>
+        <v>0.06493899762011922</v>
       </c>
       <c r="G62" t="n">
         <v>0.933913737663621</v>
@@ -3716,7 +3716,7 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0004409003538630931</v>
+        <v>0.0004409003538631933</v>
       </c>
       <c r="F64" t="n">
         <v>0.03926993004800262</v>
@@ -3739,13 +3739,13 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0008665184246429166</v>
+        <v>0.0008665184246433106</v>
       </c>
       <c r="F65" t="n">
-        <v>0.03474964161770017</v>
+        <v>0.03474964161770807</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9643838399577618</v>
+        <v>0.9643838399575425</v>
       </c>
     </row>
     <row r="66">
@@ -3762,10 +3762,10 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.002347784715333549</v>
+        <v>0.002347784715335151</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01560932124209755</v>
+        <v>0.01560932124210465</v>
       </c>
       <c r="G66" t="n">
         <v>0.9820428940426207</v>
@@ -3785,10 +3785,10 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0004132178743428617</v>
+        <v>0.0004132178743430496</v>
       </c>
       <c r="F67" t="n">
-        <v>0.02412027212175054</v>
+        <v>0.02412027212176151</v>
       </c>
       <c r="G67" t="n">
         <v>0.9754665100038677</v>
@@ -3808,10 +3808,10 @@
         <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0001641334973307949</v>
+        <v>0.0001641334973308695</v>
       </c>
       <c r="F68" t="n">
-        <v>0.04411760159298741</v>
+        <v>0.0441176015930175</v>
       </c>
       <c r="G68" t="n">
         <v>0.9557182649096327</v>
@@ -3831,13 +3831,13 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0003207674363288301</v>
+        <v>0.000320767436328903</v>
       </c>
       <c r="F69" t="n">
-        <v>0.08122410347239963</v>
+        <v>0.08122410347243655</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9184551290913777</v>
+        <v>0.9184551290911689</v>
       </c>
     </row>
     <row r="70">
@@ -3854,10 +3854,10 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0006050508509696854</v>
+        <v>0.0006050508509700982</v>
       </c>
       <c r="F70" t="n">
-        <v>0.07053836021459933</v>
+        <v>0.07053836021464746</v>
       </c>
       <c r="G70" t="n">
         <v>0.9288565889344536</v>
@@ -3877,10 +3877,10 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0002825206812921025</v>
+        <v>0.0002825206812923595</v>
       </c>
       <c r="F71" t="n">
-        <v>0.05217905134928388</v>
+        <v>0.05217905134931947</v>
       </c>
       <c r="G71" t="n">
         <v>0.9475384279694502</v>
@@ -3900,10 +3900,10 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0001932534703954828</v>
+        <v>0.0001932534703956586</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0449384142488258</v>
+        <v>0.04493841424885645</v>
       </c>
       <c r="G72" t="n">
         <v>0.9548683322807233</v>
@@ -3923,10 +3923,10 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0002317467957039235</v>
+        <v>0.0002317467957041342</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04467368658717154</v>
+        <v>0.04467368658719186</v>
       </c>
       <c r="G73" t="n">
         <v>0.9550945666171368</v>
@@ -3946,10 +3946,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0001621770189747077</v>
+        <v>0.0001621770189748183</v>
       </c>
       <c r="F74" t="n">
-        <v>0.04631764500780686</v>
+        <v>0.04631764500782792</v>
       </c>
       <c r="G74" t="n">
         <v>0.9535201779732607</v>
@@ -3969,10 +3969,10 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0002442483784468324</v>
+        <v>0.0002442483784469991</v>
       </c>
       <c r="F75" t="n">
-        <v>0.05726789152066745</v>
+        <v>0.05726789152070651</v>
       </c>
       <c r="G75" t="n">
         <v>0.9424878601009499</v>
@@ -3992,10 +3992,10 @@
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0002295852104630064</v>
+        <v>0.0002295852104631108</v>
       </c>
       <c r="F76" t="n">
-        <v>0.05141757844611321</v>
+        <v>0.05141757844612491</v>
       </c>
       <c r="G76" t="n">
         <v>0.9483528363433865</v>
@@ -4015,10 +4015,10 @@
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0003145371423268204</v>
+        <v>0.0003145371423271065</v>
       </c>
       <c r="F77" t="n">
-        <v>0.05946174900582452</v>
+        <v>0.05946174900586509</v>
       </c>
       <c r="G77" t="n">
         <v>0.9402237138517451</v>
@@ -4038,10 +4038,10 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0005415766600451331</v>
+        <v>0.0005415766600457487</v>
       </c>
       <c r="F78" t="n">
-        <v>0.07259719797305123</v>
+        <v>0.07259719797310074</v>
       </c>
       <c r="G78" t="n">
         <v>0.9268612253668892</v>
@@ -4061,10 +4061,10 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>0.000380298712655835</v>
+        <v>0.0003802987126560944</v>
       </c>
       <c r="F79" t="n">
-        <v>0.04972674988946517</v>
+        <v>0.04972674988949909</v>
       </c>
       <c r="G79" t="n">
         <v>0.9498929513977972</v>
@@ -4084,10 +4084,10 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0.000273601012379207</v>
+        <v>0.0002736010123792692</v>
       </c>
       <c r="F80" t="n">
-        <v>0.03943118483517535</v>
+        <v>0.03943118483519328</v>
       </c>
       <c r="G80" t="n">
         <v>0.9602952141524633</v>
@@ -4107,10 +4107,10 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0003518246580200578</v>
+        <v>0.0003518246580202977</v>
       </c>
       <c r="F81" t="n">
-        <v>0.03309183665118982</v>
+        <v>0.03309183665121239</v>
       </c>
       <c r="G81" t="n">
         <v>0.9665563386907627</v>
@@ -4130,10 +4130,10 @@
         <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0003735117532553973</v>
+        <v>0.0003735117532554822</v>
       </c>
       <c r="F82" t="n">
-        <v>0.03038208923783941</v>
+        <v>0.03038208923786013</v>
       </c>
       <c r="G82" t="n">
         <v>0.9692443990089639</v>
@@ -4153,10 +4153,10 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0003250678176888116</v>
+        <v>0.0003250678176890334</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01476779587958614</v>
+        <v>0.01476779587959622</v>
       </c>
       <c r="G83" t="n">
         <v>0.9849071363026729</v>
@@ -4176,10 +4176,10 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0002107034570702362</v>
+        <v>0.0002107034570704278</v>
       </c>
       <c r="F84" t="n">
-        <v>0.01086384085975302</v>
+        <v>0.01086384085976043</v>
       </c>
       <c r="G84" t="n">
         <v>0.9889254556831452</v>
@@ -4193,16 +4193,16 @@
         <v>0.03402946422756281</v>
       </c>
       <c r="C85" t="n">
-        <v>0.002718764958117402</v>
+        <v>0.002718764958117403</v>
       </c>
       <c r="D85" t="n">
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>7.469868100989851e-05</v>
+        <v>7.469868100994945e-05</v>
       </c>
       <c r="F85" t="n">
-        <v>0.009935620687826467</v>
+        <v>0.009935620687830986</v>
       </c>
       <c r="G85" t="n">
         <v>0.9899896806311508</v>
@@ -4213,7 +4213,7 @@
         <v>38717</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.002845288954795244</v>
+        <v>-0.002845288954795243</v>
       </c>
       <c r="C86" t="n">
         <v>0.008921207357914518</v>
@@ -4222,10 +4222,10 @@
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>6.150174602002252e-05</v>
+        <v>6.150174602007847e-05</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01009863813665259</v>
+        <v>0.01009863813665718</v>
       </c>
       <c r="G86" t="n">
         <v>0.9898398601173478</v>
@@ -4245,10 +4245,10 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.180491199776558e-05</v>
+        <v>5.180491199782448e-05</v>
       </c>
       <c r="F87" t="n">
-        <v>0.00744973265949087</v>
+        <v>0.007449732659494258</v>
       </c>
       <c r="G87" t="n">
         <v>0.9924984624286036</v>
@@ -4259,7 +4259,7 @@
         <v>38776</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.0006837315003157397</v>
+        <v>-0.0006837315003157393</v>
       </c>
       <c r="C88" t="n">
         <v>-0.004183623699470881</v>
@@ -4268,10 +4268,10 @@
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>4.278226683176838e-05</v>
+        <v>4.278226683181702e-05</v>
       </c>
       <c r="F88" t="n">
-        <v>0.006538593611185419</v>
+        <v>0.006538593611188392</v>
       </c>
       <c r="G88" t="n">
         <v>0.99341862412207</v>
@@ -4291,10 +4291,10 @@
         <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>4.2786579600595e-05</v>
+        <v>4.278657960063392e-05</v>
       </c>
       <c r="F89" t="n">
-        <v>0.006053149877037655</v>
+        <v>0.006053149877040408</v>
       </c>
       <c r="G89" t="n">
         <v>0.9939040635434653</v>
@@ -4314,10 +4314,10 @@
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>3.411982743459139e-05</v>
+        <v>3.411982743462243e-05</v>
       </c>
       <c r="F90" t="n">
-        <v>0.00873266244347588</v>
+        <v>0.008732662443483823</v>
       </c>
       <c r="G90" t="n">
         <v>0.9912332177291865</v>
@@ -4337,10 +4337,10 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>8.288546004616779e-05</v>
+        <v>8.288546004620549e-05</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01527865824908588</v>
+        <v>0.01527865824909282</v>
       </c>
       <c r="G91" t="n">
         <v>0.9846384562908831</v>
@@ -4360,10 +4360,10 @@
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>7.09519026828264e-05</v>
+        <v>7.09519026828748e-05</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01423824413971949</v>
+        <v>0.01423824413972597</v>
       </c>
       <c r="G92" t="n">
         <v>0.985690803957598</v>
@@ -4383,10 +4383,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>7.046757511700926e-05</v>
+        <v>7.046757511705732e-05</v>
       </c>
       <c r="F93" t="n">
-        <v>0.01450822716053162</v>
+        <v>0.01450822716053822</v>
       </c>
       <c r="G93" t="n">
         <v>0.9854213052643136</v>
@@ -4406,10 +4406,10 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>6.646091210869573e-05</v>
+        <v>6.646091210874107e-05</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01308879226313498</v>
+        <v>0.01308879226313796</v>
       </c>
       <c r="G94" t="n">
         <v>0.9868447468247302</v>
@@ -4429,7 +4429,7 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>4.579348746524769e-05</v>
+        <v>4.579348746526851e-05</v>
       </c>
       <c r="F95" t="n">
         <v>0.01310332477488194</v>
@@ -4452,7 +4452,7 @@
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>3.52629656674136e-05</v>
+        <v>3.526296566742162e-05</v>
       </c>
       <c r="F96" t="n">
         <v>0.01559006581828647</v>
@@ -4475,7 +4475,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>3.360945391450299e-05</v>
+        <v>3.360945391451827e-05</v>
       </c>
       <c r="F97" t="n">
         <v>0.02185420444716618</v>
@@ -4498,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>3.903310141728735e-05</v>
+        <v>3.903310141731398e-05</v>
       </c>
       <c r="F98" t="n">
         <v>0.03280679889479783</v>
@@ -4521,10 +4521,10 @@
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>3.34434882283988e-05</v>
+        <v>3.34434882284064e-05</v>
       </c>
       <c r="F99" t="n">
-        <v>0.06564756079168411</v>
+        <v>0.06564756079166918</v>
       </c>
       <c r="G99" t="n">
         <v>0.9343189957201367</v>
@@ -4544,10 +4544,10 @@
         <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>9.571055590237007e-05</v>
+        <v>9.571055590243535e-05</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1399340066148953</v>
+        <v>0.1399340066149271</v>
       </c>
       <c r="G100" t="n">
         <v>0.8599702828292093</v>
@@ -4567,7 +4567,7 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>9.839690515153312e-05</v>
+        <v>9.839690515160024e-05</v>
       </c>
       <c r="F101" t="n">
         <v>0.1540646568812124</v>
@@ -4590,10 +4590,10 @@
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>7.223044364453617e-05</v>
+        <v>7.223044364458543e-05</v>
       </c>
       <c r="F102" t="n">
-        <v>0.199593332122196</v>
+        <v>0.1995933321222414</v>
       </c>
       <c r="G102" t="n">
         <v>0.8003344374341234</v>
@@ -4613,7 +4613,7 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>8.146116532850414e-05</v>
+        <v>8.146116532854118e-05</v>
       </c>
       <c r="F103" t="n">
         <v>0.279438054975624</v>
@@ -4636,13 +4636,13 @@
         <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0001102137001563387</v>
+        <v>0.0001102137001563888</v>
       </c>
       <c r="F104" t="n">
         <v>0.4277347622598113</v>
       </c>
       <c r="G104" t="n">
-        <v>0.5721550240401221</v>
+        <v>0.5721550240399921</v>
       </c>
     </row>
     <row r="105">
@@ -4659,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0002272840911716191</v>
+        <v>0.0002272840911717224</v>
       </c>
       <c r="F105" t="n">
         <v>0.6513913383873693</v>
@@ -4682,13 +4682,13 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0001864090222118076</v>
+        <v>0.00018640902221185</v>
       </c>
       <c r="F106" t="n">
         <v>0.6757136043308102</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3240999866470438</v>
+        <v>0.3240999866469702</v>
       </c>
     </row>
     <row r="107">
@@ -4699,13 +4699,13 @@
         <v>0.03352305135437444</v>
       </c>
       <c r="C107" t="n">
-        <v>0.000268536980876533</v>
+        <v>0.0002685369808765334</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>8.404773591530452e-05</v>
+        <v>8.404773591528539e-05</v>
       </c>
       <c r="F107" t="n">
         <v>0.7212423587286666</v>
@@ -4722,19 +4722,19 @@
         <v>0.01258704390080084</v>
       </c>
       <c r="C108" t="n">
-        <v>0.007736157572576452</v>
+        <v>0.007736157572576453</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>6.953471018466546e-05</v>
+        <v>6.953471018460222e-05</v>
       </c>
       <c r="F108" t="n">
         <v>0.8169458292520808</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1829846360378385</v>
+        <v>0.1829846360377969</v>
       </c>
     </row>
     <row r="109">
@@ -4757,7 +4757,7 @@
         <v>0.9899614955471975</v>
       </c>
       <c r="G109" t="n">
-        <v>0.009819827261362575</v>
+        <v>0.009819827261360343</v>
       </c>
     </row>
     <row r="110">
@@ -4774,13 +4774,13 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0003190606560971084</v>
+        <v>0.0003190606560971809</v>
       </c>
       <c r="F110" t="n">
         <v>0.9900961120703093</v>
       </c>
       <c r="G110" t="n">
-        <v>0.009584827273627701</v>
+        <v>0.009584827273629882</v>
       </c>
     </row>
     <row r="111">
@@ -4797,13 +4797,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0008891070273006044</v>
+        <v>0.0008891070273010088</v>
       </c>
       <c r="F111" t="n">
         <v>0.9989844468510299</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0001264461216691714</v>
+        <v>0.0001264461216692001</v>
       </c>
     </row>
     <row r="112">
@@ -4820,13 +4820,13 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.001933095410176167</v>
+        <v>0.001933095410177925</v>
       </c>
       <c r="F112" t="n">
         <v>0.994919793492036</v>
       </c>
       <c r="G112" t="n">
-        <v>0.003147111097695902</v>
+        <v>0.003147111097698764</v>
       </c>
     </row>
     <row r="113">
@@ -4834,7 +4834,7 @@
         <v>39538</v>
       </c>
       <c r="B113" t="n">
-        <v>-0.006027409667488031</v>
+        <v>-0.006027409667488032</v>
       </c>
       <c r="C113" t="n">
         <v>0.01148223471221401</v>
@@ -4843,13 +4843,13 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.00490947353051409</v>
+        <v>0.004909473530516323</v>
       </c>
       <c r="F113" t="n">
         <v>0.9827419086553635</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0123486178140767</v>
+        <v>0.01234861781408512</v>
       </c>
     </row>
     <row r="114">
@@ -4866,13 +4866,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.01597879040658511</v>
+        <v>0.01597879040659237</v>
       </c>
       <c r="F114" t="n">
         <v>0.9672865709711845</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0167346386222303</v>
+        <v>0.01673463862224552</v>
       </c>
     </row>
     <row r="115">
@@ -4889,13 +4889,13 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.03554731882457184</v>
+        <v>0.03554731882457992</v>
       </c>
       <c r="F115" t="n">
         <v>0.9462318202388903</v>
       </c>
       <c r="G115" t="n">
-        <v>0.01822086093656375</v>
+        <v>0.01822086093657617</v>
       </c>
     </row>
     <row r="116">
@@ -4912,13 +4912,13 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.07207908854934506</v>
+        <v>0.07207908854937783</v>
       </c>
       <c r="F116" t="n">
         <v>0.9277550798077326</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0001658316429191319</v>
+        <v>0.000165831642919245</v>
       </c>
     </row>
     <row r="117">
@@ -4935,13 +4935,13 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.1146344350032546</v>
+        <v>0.1146344350033067</v>
       </c>
       <c r="F117" t="n">
         <v>0.8819057739810874</v>
       </c>
       <c r="G117" t="n">
-        <v>0.003459791015606608</v>
+        <v>0.003459791015609755</v>
       </c>
     </row>
     <row r="118">
@@ -4961,10 +4961,10 @@
         <v>0.2639879887743334</v>
       </c>
       <c r="F118" t="n">
-        <v>0.7338228880060652</v>
+        <v>0.7338228880058985</v>
       </c>
       <c r="G118" t="n">
-        <v>0.002189123219653413</v>
+        <v>0.002189123219654907</v>
       </c>
     </row>
     <row r="119">
@@ -4987,7 +4987,7 @@
         <v>0.2624730581810596</v>
       </c>
       <c r="G119" t="n">
-        <v>5.458576303582955e-08</v>
+        <v>5.458576303592885e-08</v>
       </c>
     </row>
     <row r="120">
@@ -5007,10 +5007,10 @@
         <v>0.9993517480391874</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0006482519607740414</v>
+        <v>0.0006482519607741887</v>
       </c>
       <c r="G120" t="n">
-        <v>2.653483819411902e-14</v>
+        <v>2.653483819412505e-14</v>
       </c>
     </row>
     <row r="121">
@@ -5027,13 +5027,13 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9999395026844889</v>
+        <v>0.9999395026844888</v>
       </c>
       <c r="F121" t="n">
-        <v>6.049728893249492e-05</v>
+        <v>6.049728893248116e-05</v>
       </c>
       <c r="G121" t="n">
-        <v>2.664064169275062e-11</v>
+        <v>2.664064169274456e-11</v>
       </c>
     </row>
     <row r="122">
@@ -5053,10 +5053,10 @@
         <v>0.9999680119242771</v>
       </c>
       <c r="F122" t="n">
-        <v>2.86959645549216e-05</v>
+        <v>2.869596455486288e-05</v>
       </c>
       <c r="G122" t="n">
-        <v>3.2921112121352e-06</v>
+        <v>3.292111212134451e-06</v>
       </c>
     </row>
     <row r="123">
@@ -5076,10 +5076,10 @@
         <v>0.9999811894888585</v>
       </c>
       <c r="F123" t="n">
-        <v>8.386422270052171e-06</v>
+        <v>8.386422270029289e-06</v>
       </c>
       <c r="G123" t="n">
-        <v>1.042408891517206e-05</v>
+        <v>1.042408891516969e-05</v>
       </c>
     </row>
     <row r="124">
@@ -5099,10 +5099,10 @@
         <v>0.9994104366366997</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0005794191739773275</v>
+        <v>0.0005794191739748244</v>
       </c>
       <c r="G124" t="n">
-        <v>1.014418924915271e-05</v>
+        <v>1.014418924914579e-05</v>
       </c>
     </row>
     <row r="125">
@@ -5122,10 +5122,10 @@
         <v>0.9754070046452166</v>
       </c>
       <c r="F125" t="n">
-        <v>0.00383555151901221</v>
+        <v>0.003835551518994768</v>
       </c>
       <c r="G125" t="n">
-        <v>0.02075744383587813</v>
+        <v>0.02075744383587342</v>
       </c>
     </row>
     <row r="126">
@@ -5142,10 +5142,10 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>0.9285427790140599</v>
+        <v>0.928542779014271</v>
       </c>
       <c r="F126" t="n">
-        <v>0.03295763141129383</v>
+        <v>0.03295763141120391</v>
       </c>
       <c r="G126" t="n">
         <v>0.03849958957459623</v>
@@ -5165,10 +5165,10 @@
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>0.4094809685643193</v>
+        <v>0.4094809685644125</v>
       </c>
       <c r="F127" t="n">
-        <v>0.04096565892810693</v>
+        <v>0.04096565892797652</v>
       </c>
       <c r="G127" t="n">
         <v>0.549553372507665</v>
@@ -5188,13 +5188,13 @@
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0905073026871635</v>
+        <v>0.09050730268716349</v>
       </c>
       <c r="F128" t="n">
-        <v>0.05156634275773619</v>
+        <v>0.05156634275759549</v>
       </c>
       <c r="G128" t="n">
-        <v>0.8579263545550352</v>
+        <v>0.8579263545552303</v>
       </c>
     </row>
     <row r="129">
@@ -5214,7 +5214,7 @@
         <v>0.04114170586732759</v>
       </c>
       <c r="F129" t="n">
-        <v>0.08302598697809924</v>
+        <v>0.08302598697796709</v>
       </c>
       <c r="G129" t="n">
         <v>0.8758323071546281</v>
@@ -5234,10 +5234,10 @@
         <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>0.007304108682429175</v>
+        <v>0.007304108682430835</v>
       </c>
       <c r="F130" t="n">
-        <v>0.09785473455151299</v>
+        <v>0.09785473455135725</v>
       </c>
       <c r="G130" t="n">
         <v>0.8948411567661206</v>
@@ -5257,10 +5257,10 @@
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>0.001653311260694146</v>
+        <v>0.001653311260694522</v>
       </c>
       <c r="F131" t="n">
-        <v>0.132829951271664</v>
+        <v>0.132829951271513</v>
       </c>
       <c r="G131" t="n">
         <v>0.8655167374677221</v>
@@ -5280,13 +5280,13 @@
         <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0007482490345576532</v>
+        <v>0.0007482490345579935</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2015020456813984</v>
+        <v>0.2015020456813068</v>
       </c>
       <c r="G132" t="n">
-        <v>0.7977497052840121</v>
+        <v>0.7977497052841934</v>
       </c>
     </row>
     <row r="133">
@@ -5303,13 +5303,13 @@
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0006705296937510644</v>
+        <v>0.0006705296937512169</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2734502335265653</v>
+        <v>0.2734502335265031</v>
       </c>
       <c r="G133" t="n">
-        <v>0.7258792367796516</v>
+        <v>0.7258792367798166</v>
       </c>
     </row>
     <row r="134">
@@ -5326,13 +5326,13 @@
         <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0008160869866635479</v>
+        <v>0.0008160869866633623</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3968788938298577</v>
+        <v>0.3968788938297675</v>
       </c>
       <c r="G134" t="n">
-        <v>0.6023050191835232</v>
+        <v>0.6023050191836602</v>
       </c>
     </row>
     <row r="135">
@@ -5349,13 +5349,13 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0006173717726427738</v>
+        <v>0.0006173717726430546</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7554549501170271</v>
+        <v>0.7554549501168554</v>
       </c>
       <c r="G135" t="n">
-        <v>0.2439276781104218</v>
+        <v>0.2439276781105327</v>
       </c>
     </row>
     <row r="136">
@@ -5378,7 +5378,7 @@
         <v>0.7872761088026886</v>
       </c>
       <c r="G136" t="n">
-        <v>0.2125661531182555</v>
+        <v>0.2125661531183522</v>
       </c>
     </row>
     <row r="137">
@@ -5395,13 +5395,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0001269621452166726</v>
+        <v>0.0001269621452167015</v>
       </c>
       <c r="F137" t="n">
         <v>0.8637468646493833</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1361261732052913</v>
+        <v>0.1361261732053532</v>
       </c>
     </row>
     <row r="138">
@@ -5418,13 +5418,13 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0001037301409884672</v>
+        <v>0.0001037301409883729</v>
       </c>
       <c r="F138" t="n">
         <v>0.9131911143395174</v>
       </c>
       <c r="G138" t="n">
-        <v>0.08670515551952555</v>
+        <v>0.08670515551954527</v>
       </c>
     </row>
     <row r="139">
@@ -5464,13 +5464,13 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0005638577952093096</v>
+        <v>0.0005638577952096943</v>
       </c>
       <c r="F140" t="n">
         <v>0.9993611370129672</v>
       </c>
       <c r="G140" t="n">
-        <v>7.500519189363368e-05</v>
+        <v>7.500519189366778e-05</v>
       </c>
     </row>
     <row r="141">
@@ -5487,13 +5487,13 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.001066134877131409</v>
+        <v>0.001066134877132136</v>
       </c>
       <c r="F141" t="n">
         <v>0.996071924995468</v>
       </c>
       <c r="G141" t="n">
-        <v>0.002861940127341208</v>
+        <v>0.00286194012734316</v>
       </c>
     </row>
     <row r="142">
@@ -5510,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0.002142849654130068</v>
+        <v>0.002142849654132504</v>
       </c>
       <c r="F142" t="n">
-        <v>0.9969835896528572</v>
+        <v>0.9969835896528573</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0008735606929273301</v>
+        <v>0.000873560692927926</v>
       </c>
     </row>
     <row r="143">
@@ -5533,13 +5533,13 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0.003210258594497339</v>
+        <v>0.003210258594498799</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9794825307587941</v>
+        <v>0.9794825307585714</v>
       </c>
       <c r="G143" t="n">
-        <v>0.01730721064681948</v>
+        <v>0.01730721064682735</v>
       </c>
     </row>
     <row r="144">
@@ -5556,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0.00155757705996972</v>
+        <v>0.001557577059970074</v>
       </c>
       <c r="F144" t="n">
-        <v>0.9181030928200622</v>
+        <v>0.9181030928198534</v>
       </c>
       <c r="G144" t="n">
-        <v>0.08033933012008067</v>
+        <v>0.08033933012009893</v>
       </c>
     </row>
     <row r="145">
@@ -5579,13 +5579,13 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>0.002039832932719513</v>
+        <v>0.002039832932720905</v>
       </c>
       <c r="F145" t="n">
         <v>0.8872066205468251</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1107535465204272</v>
+        <v>0.1107535465205028</v>
       </c>
     </row>
     <row r="146">
@@ -5602,13 +5602,13 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0.004643889915735652</v>
+        <v>0.004643889915737764</v>
       </c>
       <c r="F146" t="n">
         <v>0.8849692155105978</v>
       </c>
       <c r="G146" t="n">
-        <v>0.110386894573623</v>
+        <v>0.1103868945736983</v>
       </c>
     </row>
     <row r="147">
@@ -5625,13 +5625,13 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.001108786340424749</v>
+        <v>0.001108786340425001</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8209873425459961</v>
+        <v>0.8209873425458094</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1779038711136594</v>
+        <v>0.1779038711136998</v>
       </c>
     </row>
     <row r="148">
@@ -5648,13 +5648,13 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0004211530235227325</v>
+        <v>0.000421153023522924</v>
       </c>
       <c r="F148" t="n">
-        <v>0.7985225741878209</v>
+        <v>0.7985225741876394</v>
       </c>
       <c r="G148" t="n">
-        <v>0.2010562727886945</v>
+        <v>0.2010562727887402</v>
       </c>
     </row>
     <row r="149">
@@ -5674,10 +5674,10 @@
         <v>0.0002052697171583846</v>
       </c>
       <c r="F149" t="n">
-        <v>0.802532182465847</v>
+        <v>0.8025321824656646</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1972625478169432</v>
+        <v>0.1972625478170778</v>
       </c>
     </row>
     <row r="150">
@@ -5694,13 +5694,13 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0001363881107499346</v>
+        <v>0.0001363881107498726</v>
       </c>
       <c r="F150" t="n">
         <v>0.8332453192405153</v>
       </c>
       <c r="G150" t="n">
-        <v>0.1666182926486948</v>
+        <v>0.1666182926488464</v>
       </c>
     </row>
     <row r="151">
@@ -5723,7 +5723,7 @@
         <v>0.9063066231242313</v>
       </c>
       <c r="G151" t="n">
-        <v>0.09351087870742689</v>
+        <v>0.09351087870751193</v>
       </c>
     </row>
     <row r="152">
@@ -5740,13 +5740,13 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0002107751815920247</v>
+        <v>0.0002107751815919767</v>
       </c>
       <c r="F152" t="n">
-        <v>0.9381055173605196</v>
+        <v>0.9381055173603063</v>
       </c>
       <c r="G152" t="n">
-        <v>0.06168370745797801</v>
+        <v>0.06168370745802008</v>
       </c>
     </row>
     <row r="153">
@@ -5763,13 +5763,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0004834227018208997</v>
+        <v>0.0004834227018207899</v>
       </c>
       <c r="F153" t="n">
-        <v>0.9879257438143204</v>
+        <v>0.9879257438140958</v>
       </c>
       <c r="G153" t="n">
-        <v>0.01159083348397223</v>
+        <v>0.0115908334839775</v>
       </c>
     </row>
     <row r="154">
@@ -5792,7 +5792,7 @@
         <v>0.9988044057120223</v>
       </c>
       <c r="G154" t="n">
-        <v>3.56108732622201e-05</v>
+        <v>3.56108732622282e-05</v>
       </c>
     </row>
     <row r="155">
@@ -5809,13 +5809,13 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0.001778341099366319</v>
+        <v>0.001778341099367128</v>
       </c>
       <c r="F155" t="n">
         <v>0.9981978940312338</v>
       </c>
       <c r="G155" t="n">
-        <v>2.376486936684559e-05</v>
+        <v>2.37648693668564e-05</v>
       </c>
     </row>
     <row r="156">
@@ -5832,13 +5832,13 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.003102786398365804</v>
+        <v>0.003102786398367921</v>
       </c>
       <c r="F156" t="n">
         <v>0.9955707184760517</v>
       </c>
       <c r="G156" t="n">
-        <v>0.001326495125566449</v>
+        <v>0.001326495125567354</v>
       </c>
     </row>
     <row r="157">
@@ -5855,13 +5855,13 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>0.001363774787687299</v>
+        <v>0.00136377478768854</v>
       </c>
       <c r="F157" t="n">
         <v>0.9453092691989441</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05332695601327681</v>
+        <v>0.05332695601333743</v>
       </c>
     </row>
     <row r="158">
@@ -5878,13 +5878,13 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0008640778468410193</v>
+        <v>0.0008640778468414122</v>
       </c>
       <c r="F158" t="n">
         <v>0.9077070048869074</v>
       </c>
       <c r="G158" t="n">
-        <v>0.09142891726618071</v>
+        <v>0.09142891726622229</v>
       </c>
     </row>
     <row r="159">
@@ -5901,13 +5901,13 @@
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0006148861219130672</v>
+        <v>0.000614886121913207</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8870008117335655</v>
+        <v>0.8870008117333639</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1123843021445775</v>
+        <v>0.1123843021446286</v>
       </c>
     </row>
     <row r="160">
@@ -5924,13 +5924,13 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>0.000748738525732374</v>
+        <v>0.0007487385257325442</v>
       </c>
       <c r="F160" t="n">
         <v>0.8870984404481879</v>
       </c>
       <c r="G160" t="n">
-        <v>0.1121528210259937</v>
+        <v>0.1121528210260447</v>
       </c>
     </row>
     <row r="161">
@@ -5953,7 +5953,7 @@
         <v>0.8996713401154236</v>
       </c>
       <c r="G161" t="n">
-        <v>0.09857894287473265</v>
+        <v>0.09857894287477748</v>
       </c>
     </row>
     <row r="162">
@@ -5993,13 +5993,13 @@
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0127665461717268</v>
+        <v>0.0127665461717239</v>
       </c>
       <c r="F163" t="n">
         <v>0.9502752339313474</v>
       </c>
       <c r="G163" t="n">
-        <v>0.03695821989700777</v>
+        <v>0.03695821989699937</v>
       </c>
     </row>
     <row r="164">
@@ -6016,13 +6016,13 @@
         <v>2</v>
       </c>
       <c r="E164" t="n">
-        <v>0.006188983478466329</v>
+        <v>0.006188983478464922</v>
       </c>
       <c r="F164" t="n">
         <v>0.5853291605065929</v>
       </c>
       <c r="G164" t="n">
-        <v>0.408481856014998</v>
+        <v>0.4084818560149051</v>
       </c>
     </row>
     <row r="165">
@@ -6039,7 +6039,7 @@
         <v>2</v>
       </c>
       <c r="E165" t="n">
-        <v>0.003518002919415154</v>
+        <v>0.003518002919416754</v>
       </c>
       <c r="F165" t="n">
         <v>0.3480932550937806</v>
@@ -6085,10 +6085,10 @@
         <v>2</v>
       </c>
       <c r="E167" t="n">
-        <v>0.0009298463360981708</v>
+        <v>0.0009298463360985936</v>
       </c>
       <c r="F167" t="n">
-        <v>0.1281569020998531</v>
+        <v>0.1281569020998823</v>
       </c>
       <c r="G167" t="n">
         <v>0.8709132515639891</v>
@@ -6108,7 +6108,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0009222514486593336</v>
+        <v>0.0009222514486597529</v>
       </c>
       <c r="F168" t="n">
         <v>0.09338824851342983</v>
@@ -6131,10 +6131,10 @@
         <v>2</v>
       </c>
       <c r="E169" t="n">
-        <v>0.0005238483410196904</v>
+        <v>0.0005238483410199286</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0637625874109925</v>
+        <v>0.06376258741100699</v>
       </c>
       <c r="G169" t="n">
         <v>0.9357135642479668</v>
@@ -6154,10 +6154,10 @@
         <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0003376358171868194</v>
+        <v>0.0003376358171868962</v>
       </c>
       <c r="F170" t="n">
-        <v>0.04307451008013353</v>
+        <v>0.04307451008014332</v>
       </c>
       <c r="G170" t="n">
         <v>0.9565878541026505</v>
@@ -6177,10 +6177,10 @@
         <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0003631320667215652</v>
+        <v>0.0003631320667216478</v>
       </c>
       <c r="F171" t="n">
-        <v>0.03726646102711639</v>
+        <v>0.03726646102712487</v>
       </c>
       <c r="G171" t="n">
         <v>0.9623704069062662</v>
@@ -6223,10 +6223,10 @@
         <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0001491926901978694</v>
+        <v>0.0001491926901979034</v>
       </c>
       <c r="F173" t="n">
-        <v>0.01654761161468359</v>
+        <v>0.01654761161468735</v>
       </c>
       <c r="G173" t="n">
         <v>0.9833031956951509</v>
@@ -6246,10 +6246,10 @@
         <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0001496695743154346</v>
+        <v>0.0001496695743155367</v>
       </c>
       <c r="F174" t="n">
-        <v>0.01179200767225145</v>
+        <v>0.01179200767225681</v>
       </c>
       <c r="G174" t="n">
         <v>0.988058322753437</v>
@@ -6269,10 +6269,10 @@
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0002675890898981636</v>
+        <v>0.0002675890898982853</v>
       </c>
       <c r="F175" t="n">
-        <v>0.008301844510009414</v>
+        <v>0.008301844510011301</v>
       </c>
       <c r="G175" t="n">
         <v>0.9914305664000076</v>
@@ -6292,10 +6292,10 @@
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0001735735607631605</v>
+        <v>0.0001735735607633183</v>
       </c>
       <c r="F176" t="n">
-        <v>0.00784973714206672</v>
+        <v>0.00784973714207029</v>
       </c>
       <c r="G176" t="n">
         <v>0.9919766892971755</v>
@@ -6315,10 +6315,10 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>8.258186738664228e-05</v>
+        <v>8.258186738667983e-05</v>
       </c>
       <c r="F177" t="n">
-        <v>0.01447744430697494</v>
+        <v>0.01447744430697823</v>
       </c>
       <c r="G177" t="n">
         <v>0.985439973825614</v>
@@ -6338,7 +6338,7 @@
         <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0001298110055543515</v>
+        <v>0.000129811005554381</v>
       </c>
       <c r="F178" t="n">
         <v>0.01831766066783268</v>
@@ -6361,10 +6361,10 @@
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>7.584224213444698e-05</v>
+        <v>7.584224213448147e-05</v>
       </c>
       <c r="F179" t="n">
-        <v>0.02128302314101983</v>
+        <v>0.02128302314102466</v>
       </c>
       <c r="G179" t="n">
         <v>0.9786411346169052</v>
@@ -6384,10 +6384,10 @@
         <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>6.253423996920127e-05</v>
+        <v>6.253423996927235e-05</v>
       </c>
       <c r="F180" t="n">
-        <v>0.02936913881872209</v>
+        <v>0.02936913881873544</v>
       </c>
       <c r="G180" t="n">
         <v>0.970568326941291</v>
@@ -6407,10 +6407,10 @@
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>7.462082264547029e-05</v>
+        <v>7.462082264553816e-05</v>
       </c>
       <c r="F181" t="n">
-        <v>0.04276562906505239</v>
+        <v>0.04276562906508156</v>
       </c>
       <c r="G181" t="n">
         <v>0.9571597501123275</v>
@@ -6430,13 +6430,13 @@
         <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0002133082438159932</v>
+        <v>0.0002133082438161872</v>
       </c>
       <c r="F182" t="n">
-        <v>0.06872962147793722</v>
+        <v>0.06872962147795285</v>
       </c>
       <c r="G182" t="n">
-        <v>0.9310570702783323</v>
+        <v>0.9310570702781206</v>
       </c>
     </row>
     <row r="183">
@@ -6453,13 +6453,13 @@
         <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>0.000703296634764209</v>
+        <v>0.0007032966347646887</v>
       </c>
       <c r="F183" t="n">
-        <v>0.1241747993869829</v>
+        <v>0.1241747993870393</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8751219039783245</v>
+        <v>0.8751219039781255</v>
       </c>
     </row>
     <row r="184">
@@ -6476,7 +6476,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0006499937349041844</v>
+        <v>0.00064999373490448</v>
       </c>
       <c r="F184" t="n">
         <v>0.07980482744118557</v>
@@ -6499,7 +6499,7 @@
         <v>2</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0003547659418676078</v>
+        <v>0.0003547659418677692</v>
       </c>
       <c r="F185" t="n">
         <v>0.05157543465533498</v>
@@ -6522,10 +6522,10 @@
         <v>2</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0002207295689942342</v>
+        <v>0.0002207295689943848</v>
       </c>
       <c r="F186" t="n">
-        <v>0.04094182096838094</v>
+        <v>0.04094182096837163</v>
       </c>
       <c r="G186" t="n">
         <v>0.9588374494626516</v>
@@ -6545,7 +6545,7 @@
         <v>2</v>
       </c>
       <c r="E187" t="n">
-        <v>0.0001830076221282555</v>
+        <v>0.0001830076221283803</v>
       </c>
       <c r="F187" t="n">
         <v>0.0354414052357124</v>
@@ -6568,7 +6568,7 @@
         <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>9.247656921410639e-05</v>
+        <v>9.247656921416947e-05</v>
       </c>
       <c r="F188" t="n">
         <v>0.03575948257217969</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="E189" t="n">
-        <v>9.575619502660944e-05</v>
+        <v>9.575619502667476e-05</v>
       </c>
       <c r="F189" t="n">
-        <v>0.04518339051626553</v>
+        <v>0.04518339051624498</v>
       </c>
       <c r="G189" t="n">
         <v>0.9547208532886526</v>
@@ -6614,10 +6614,10 @@
         <v>2</v>
       </c>
       <c r="E190" t="n">
-        <v>9.483807469327464e-05</v>
+        <v>9.483807469338246e-05</v>
       </c>
       <c r="F190" t="n">
-        <v>0.05785624065892917</v>
+        <v>0.05785624065891602</v>
       </c>
       <c r="G190" t="n">
         <v>0.9420489212662947</v>
@@ -6637,10 +6637,10 @@
         <v>2</v>
       </c>
       <c r="E191" t="n">
-        <v>7.353822937449662e-05</v>
+        <v>7.353822937453007e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0.08648052651499628</v>
+        <v>0.0864805265149373</v>
       </c>
       <c r="G191" t="n">
         <v>0.9134459352557309</v>
@@ -6660,10 +6660,10 @@
         <v>2</v>
       </c>
       <c r="E192" t="n">
-        <v>4.852217599474399e-05</v>
+        <v>4.852217599476605e-05</v>
       </c>
       <c r="F192" t="n">
-        <v>0.1441176330311399</v>
+        <v>0.1441176330310743</v>
       </c>
       <c r="G192" t="n">
         <v>0.8558338447929376</v>
@@ -6683,10 +6683,10 @@
         <v>2</v>
       </c>
       <c r="E193" t="n">
-        <v>6.161814875696546e-05</v>
+        <v>6.161814875699348e-05</v>
       </c>
       <c r="F193" t="n">
-        <v>0.2485316404853315</v>
+        <v>0.248531640485275</v>
       </c>
       <c r="G193" t="n">
         <v>0.7514067413658614</v>
@@ -6706,7 +6706,7 @@
         <v>2</v>
       </c>
       <c r="E194" t="n">
-        <v>0.0002076448916403956</v>
+        <v>0.0002076448916406317</v>
       </c>
       <c r="F194" t="n">
         <v>0.4441502682001394</v>
@@ -6729,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.001188429379809854</v>
+        <v>0.001188429379810934</v>
       </c>
       <c r="F195" t="n">
         <v>0.7454039332490188</v>
@@ -6752,7 +6752,7 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.001895392689999839</v>
+        <v>0.001895392690000701</v>
       </c>
       <c r="F196" t="n">
         <v>0.7373630576968607</v>
@@ -6775,7 +6775,7 @@
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>0.001381329606965887</v>
+        <v>0.001381329606967144</v>
       </c>
       <c r="F197" t="n">
         <v>0.7032998760950835</v>
@@ -6798,13 +6798,13 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0006052859701157873</v>
+        <v>0.0006052859701163377</v>
       </c>
       <c r="F198" t="n">
         <v>0.6569682528349239</v>
       </c>
       <c r="G198" t="n">
-        <v>0.3424264611948644</v>
+        <v>0.3424264611950202</v>
       </c>
     </row>
     <row r="199">
@@ -6821,13 +6821,13 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0002841298677603908</v>
+        <v>0.0002841298677604553</v>
       </c>
       <c r="F199" t="n">
-        <v>0.6533730543518746</v>
+        <v>0.6533730543517261</v>
       </c>
       <c r="G199" t="n">
-        <v>0.3463428157803662</v>
+        <v>0.3463428157804449</v>
       </c>
     </row>
     <row r="200">
@@ -6850,7 +6850,7 @@
         <v>0.6863590526092219</v>
       </c>
       <c r="G200" t="n">
-        <v>0.3133753761422525</v>
+        <v>0.313375376142395</v>
       </c>
     </row>
     <row r="201">
@@ -6873,7 +6873,7 @@
         <v>0.7845770010456131</v>
       </c>
       <c r="G201" t="n">
-        <v>0.2152802235562095</v>
+        <v>0.2152802235563074</v>
       </c>
     </row>
     <row r="202">
@@ -6896,7 +6896,7 @@
         <v>0.9683904834741623</v>
       </c>
       <c r="G202" t="n">
-        <v>0.03128341113937426</v>
+        <v>0.03128341113938137</v>
       </c>
     </row>
     <row r="203">
@@ -6913,13 +6913,13 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0004589853595238322</v>
+        <v>0.0004589853595241453</v>
       </c>
       <c r="F203" t="n">
         <v>0.9798591465998399</v>
       </c>
       <c r="G203" t="n">
-        <v>0.0196818680405448</v>
+        <v>0.01968186804055375</v>
       </c>
     </row>
     <row r="204">
@@ -6936,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0009344805802594848</v>
+        <v>0.0009344805802599098</v>
       </c>
       <c r="F204" t="n">
         <v>0.9805245726094992</v>
@@ -6959,13 +6959,13 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>0.00110550173794082</v>
+        <v>0.001105501737941575</v>
       </c>
       <c r="F205" t="n">
         <v>0.9631180395350198</v>
       </c>
       <c r="G205" t="n">
-        <v>0.03577645872693911</v>
+        <v>0.03577645872694724</v>
       </c>
     </row>
     <row r="206">
@@ -6982,13 +6982,13 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>0.002790198959935097</v>
+        <v>0.002790198959936366</v>
       </c>
       <c r="F206" t="n">
         <v>0.9627570030435757</v>
       </c>
       <c r="G206" t="n">
-        <v>0.03445279799655903</v>
+        <v>0.03445279799656686</v>
       </c>
     </row>
     <row r="207">
@@ -7005,13 +7005,13 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>0.007693038354496637</v>
+        <v>0.007693038354498387</v>
       </c>
       <c r="F207" t="n">
         <v>0.9692475999909059</v>
       </c>
       <c r="G207" t="n">
-        <v>0.02305936165455353</v>
+        <v>0.02305936165454304</v>
       </c>
     </row>
     <row r="208">
@@ -7028,13 +7028,13 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>0.005954557462829069</v>
+        <v>0.005954557462831776</v>
       </c>
       <c r="F208" t="n">
         <v>0.7863356006952522</v>
       </c>
       <c r="G208" t="n">
-        <v>0.2077098418418204</v>
+        <v>0.2077098418418676</v>
       </c>
     </row>
     <row r="209">
@@ -7074,13 +7074,13 @@
         <v>2</v>
       </c>
       <c r="E210" t="n">
-        <v>0.00323353546165453</v>
+        <v>0.003233535461656</v>
       </c>
       <c r="F210" t="n">
         <v>0.3737417299770265</v>
       </c>
       <c r="G210" t="n">
-        <v>0.6230247345612673</v>
+        <v>0.6230247345614089</v>
       </c>
     </row>
     <row r="211">
@@ -7100,7 +7100,7 @@
         <v>0.002047330410590094</v>
       </c>
       <c r="F211" t="n">
-        <v>0.2453160168712731</v>
+        <v>0.2453160168712173</v>
       </c>
       <c r="G211" t="n">
         <v>0.752636652718131</v>
@@ -7120,7 +7120,7 @@
         <v>2</v>
       </c>
       <c r="E212" t="n">
-        <v>0.003110041108907613</v>
+        <v>0.00311004110890832</v>
       </c>
       <c r="F212" t="n">
         <v>0.1833199147609035</v>
@@ -7146,7 +7146,7 @@
         <v>0.001274775957609388</v>
       </c>
       <c r="F213" t="n">
-        <v>0.1014766665288299</v>
+        <v>0.1014766665288069</v>
       </c>
       <c r="G213" t="n">
         <v>0.8972485575134796</v>
@@ -7172,7 +7172,7 @@
         <v>0.05506019832040061</v>
       </c>
       <c r="G214" t="n">
-        <v>0.9442171452551</v>
+        <v>0.9442171452551001</v>
       </c>
     </row>
     <row r="215">
@@ -7189,7 +7189,7 @@
         <v>2</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0005249626879021201</v>
+        <v>0.0005249626879022394</v>
       </c>
       <c r="F215" t="n">
         <v>0.03519333487233127</v>
@@ -7212,10 +7212,10 @@
         <v>2</v>
       </c>
       <c r="E216" t="n">
-        <v>0.0008923022251060622</v>
+        <v>0.0008923022251062652</v>
       </c>
       <c r="F216" t="n">
-        <v>0.02304217346431555</v>
+        <v>0.0230421734643208</v>
       </c>
       <c r="G216" t="n">
         <v>0.9760655243105852</v>
@@ -7258,7 +7258,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>0.0002485894593080582</v>
+        <v>0.0002485894593081147</v>
       </c>
       <c r="F218" t="n">
         <v>0.01205560826804132</v>
@@ -7281,10 +7281,10 @@
         <v>2</v>
       </c>
       <c r="E219" t="n">
-        <v>7.722434936149572e-05</v>
+        <v>7.722434936151327e-05</v>
       </c>
       <c r="F219" t="n">
-        <v>0.009447173445438441</v>
+        <v>0.009447173445440589</v>
       </c>
       <c r="G219" t="n">
         <v>0.990475602205212</v>
@@ -7304,10 +7304,10 @@
         <v>2</v>
       </c>
       <c r="E220" t="n">
-        <v>5.20378165503341e-05</v>
+        <v>5.203781655035776e-05</v>
       </c>
       <c r="F220" t="n">
-        <v>0.008756085804099438</v>
+        <v>0.00875608580410342</v>
       </c>
       <c r="G220" t="n">
         <v>0.9911918763793676</v>
@@ -7327,10 +7327,10 @@
         <v>2</v>
       </c>
       <c r="E221" t="n">
-        <v>4.195196554098243e-05</v>
+        <v>4.195196554100151e-05</v>
       </c>
       <c r="F221" t="n">
-        <v>0.008596978782686213</v>
+        <v>0.008596978782688168</v>
       </c>
       <c r="G221" t="n">
         <v>0.9913610692516946</v>
@@ -7350,10 +7350,10 @@
         <v>2</v>
       </c>
       <c r="E222" t="n">
-        <v>4.113248589836443e-05</v>
+        <v>4.113248589839248e-05</v>
       </c>
       <c r="F222" t="n">
-        <v>0.008704550048400719</v>
+        <v>0.008704550048404676</v>
       </c>
       <c r="G222" t="n">
         <v>0.9912543174657215</v>
@@ -7373,10 +7373,10 @@
         <v>2</v>
       </c>
       <c r="E223" t="n">
-        <v>3.840593538339791e-05</v>
+        <v>3.840593538341538e-05</v>
       </c>
       <c r="F223" t="n">
-        <v>0.008146369762093614</v>
+        <v>0.008146369762097318</v>
       </c>
       <c r="G223" t="n">
         <v>0.9918152243025053</v>
@@ -7396,10 +7396,10 @@
         <v>2</v>
       </c>
       <c r="E224" t="n">
-        <v>3.466877498590178e-05</v>
+        <v>3.466877498592543e-05</v>
       </c>
       <c r="F224" t="n">
-        <v>0.007756517338906258</v>
+        <v>0.007756517338909786</v>
       </c>
       <c r="G224" t="n">
         <v>0.9922088138860519</v>
@@ -7419,10 +7419,10 @@
         <v>2</v>
       </c>
       <c r="E225" t="n">
-        <v>2.776020041507461e-05</v>
+        <v>2.776020041509354e-05</v>
       </c>
       <c r="F225" t="n">
-        <v>0.00937908908387243</v>
+        <v>0.009379089083876696</v>
       </c>
       <c r="G225" t="n">
         <v>0.9905931507157884</v>
@@ -7442,10 +7442,10 @@
         <v>2</v>
       </c>
       <c r="E226" t="n">
-        <v>4.052974556632898e-05</v>
+        <v>4.052974556635662e-05</v>
       </c>
       <c r="F226" t="n">
-        <v>0.01280563297683014</v>
+        <v>0.01280563297683305</v>
       </c>
       <c r="G226" t="n">
         <v>0.9871538372775995</v>
@@ -7465,10 +7465,10 @@
         <v>2</v>
       </c>
       <c r="E227" t="n">
-        <v>4.466782449861793e-05</v>
+        <v>4.466782449863824e-05</v>
       </c>
       <c r="F227" t="n">
-        <v>0.01369704723051464</v>
+        <v>0.01369704723051153</v>
       </c>
       <c r="G227" t="n">
         <v>0.9862582849449137</v>
@@ -7488,10 +7488,10 @@
         <v>2</v>
       </c>
       <c r="E228" t="n">
-        <v>2.77104612381555e-05</v>
+        <v>2.77104612381807e-05</v>
       </c>
       <c r="F228" t="n">
-        <v>0.01994058436725608</v>
+        <v>0.01994058436726062</v>
       </c>
       <c r="G228" t="n">
         <v>0.9800317051715818</v>
@@ -7511,7 +7511,7 @@
         <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>2.844039598703394e-05</v>
+        <v>2.844039598705333e-05</v>
       </c>
       <c r="F229" t="n">
         <v>0.03343401534678729</v>
@@ -7528,19 +7528,19 @@
         <v>0.01015736928597801</v>
       </c>
       <c r="C230" t="n">
-        <v>0.001216387825317767</v>
+        <v>0.001216387825317766</v>
       </c>
       <c r="D230" t="n">
         <v>2</v>
       </c>
       <c r="E230" t="n">
-        <v>5.401179706793909e-05</v>
+        <v>5.401179706795137e-05</v>
       </c>
       <c r="F230" t="n">
         <v>0.05887151700987528</v>
       </c>
       <c r="G230" t="n">
-        <v>0.9410744711931689</v>
+        <v>0.9410744711929548</v>
       </c>
     </row>
     <row r="231">
@@ -7557,10 +7557,10 @@
         <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0002421186978465244</v>
+        <v>0.0002421186978466896</v>
       </c>
       <c r="F231" t="n">
-        <v>0.1068873890333934</v>
+        <v>0.1068873890334177</v>
       </c>
       <c r="G231" t="n">
         <v>0.8928704922687333</v>
@@ -7580,10 +7580,10 @@
         <v>2</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0006769379784255184</v>
+        <v>0.0006769379784259802</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1270896861297703</v>
+        <v>0.1270896861297992</v>
       </c>
       <c r="G232" t="n">
         <v>0.8722333758917604</v>
@@ -7603,13 +7603,13 @@
         <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0007344047723129507</v>
+        <v>0.0007344047723137856</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1393256979788646</v>
+        <v>0.1393256979788963</v>
       </c>
       <c r="G233" t="n">
-        <v>0.8599398972488813</v>
+        <v>0.8599398972486858</v>
       </c>
     </row>
     <row r="234">
@@ -7626,7 +7626,7 @@
         <v>2</v>
       </c>
       <c r="E234" t="n">
-        <v>0.0004157880814369539</v>
+        <v>0.0004157880814372375</v>
       </c>
       <c r="F234" t="n">
         <v>0.1165818168450048</v>
@@ -7649,13 +7649,13 @@
         <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>0.0001667703310803656</v>
+        <v>0.0001667703310805173</v>
       </c>
       <c r="F235" t="n">
-        <v>0.1216091532710752</v>
+        <v>0.1216091532710476</v>
       </c>
       <c r="G235" t="n">
-        <v>0.8782240763979028</v>
+        <v>0.8782240763979027</v>
       </c>
     </row>
     <row r="236">
@@ -7663,22 +7663,22 @@
         <v>43281</v>
       </c>
       <c r="B236" t="n">
-        <v>0.004736567679959356</v>
+        <v>0.004736567679959355</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.0008148956246944808</v>
+        <v>-0.000814895624694481</v>
       </c>
       <c r="D236" t="n">
         <v>2</v>
       </c>
       <c r="E236" t="n">
-        <v>8.663588604796734e-05</v>
+        <v>8.663588604800673e-05</v>
       </c>
       <c r="F236" t="n">
-        <v>0.1447771707096541</v>
+        <v>0.1447771707096212</v>
       </c>
       <c r="G236" t="n">
-        <v>0.8551361934042062</v>
+        <v>0.8551361934044007</v>
       </c>
     </row>
     <row r="237">
@@ -7695,13 +7695,13 @@
         <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>5.958845689242201e-05</v>
+        <v>5.958845689243556e-05</v>
       </c>
       <c r="F237" t="n">
         <v>0.1958391645744436</v>
       </c>
       <c r="G237" t="n">
-        <v>0.8041012469685713</v>
+        <v>0.8041012469687542</v>
       </c>
     </row>
     <row r="238">
@@ -7718,13 +7718,13 @@
         <v>2</v>
       </c>
       <c r="E238" t="n">
-        <v>5.327603143496242e-05</v>
+        <v>5.32760314349503e-05</v>
       </c>
       <c r="F238" t="n">
-        <v>0.285079736470867</v>
+        <v>0.2850797364708022</v>
       </c>
       <c r="G238" t="n">
-        <v>0.7148669874976014</v>
+        <v>0.7148669874977639</v>
       </c>
     </row>
     <row r="239">
@@ -7741,10 +7741,10 @@
         <v>2</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0001131892774728078</v>
+        <v>0.0001131892774727821</v>
       </c>
       <c r="F239" t="n">
-        <v>0.4568631582444219</v>
+        <v>0.456863158244318</v>
       </c>
       <c r="G239" t="n">
         <v>0.5430236524781049</v>
@@ -7764,10 +7764,10 @@
         <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0003788936943879895</v>
+        <v>0.0003788936943880757</v>
       </c>
       <c r="F240" t="n">
-        <v>0.9072759788584775</v>
+        <v>0.9072759788586838</v>
       </c>
       <c r="G240" t="n">
         <v>0.09234512744702757</v>
@@ -7793,7 +7793,7 @@
         <v>0.9369169016504396</v>
       </c>
       <c r="G241" t="n">
-        <v>0.0626722303019502</v>
+        <v>0.06267223030192171</v>
       </c>
     </row>
     <row r="242">
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.001108380920148156</v>
+        <v>0.001108380920149165</v>
       </c>
       <c r="F242" t="n">
         <v>0.998809557191684</v>
@@ -7833,13 +7833,13 @@
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>0.001100539497594914</v>
+        <v>0.001100539497595414</v>
       </c>
       <c r="F243" t="n">
-        <v>0.9845925181213212</v>
+        <v>0.9845925181210973</v>
       </c>
       <c r="G243" t="n">
-        <v>0.01430694238118924</v>
+        <v>0.01430694238120225</v>
       </c>
     </row>
     <row r="244">
@@ -7856,13 +7856,13 @@
         <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>0.0004013526486531578</v>
+        <v>0.0004013526486533402</v>
       </c>
       <c r="F244" t="n">
         <v>0.9644423320087703</v>
       </c>
       <c r="G244" t="n">
-        <v>0.03515631534256344</v>
+        <v>0.03515631534259542</v>
       </c>
     </row>
     <row r="245">
@@ -7879,13 +7879,13 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.000413352134304339</v>
+        <v>0.000413352134304527</v>
       </c>
       <c r="F245" t="n">
         <v>0.962055269344902</v>
       </c>
       <c r="G245" t="n">
-        <v>0.03753137852079383</v>
+        <v>0.03753137852082796</v>
       </c>
     </row>
     <row r="246">
@@ -7902,13 +7902,13 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.0006457849399233456</v>
+        <v>0.0006457849399237861</v>
       </c>
       <c r="F246" t="n">
         <v>0.9716503306199539</v>
       </c>
       <c r="G246" t="n">
-        <v>0.02770388444009785</v>
+        <v>0.02770388444011675</v>
       </c>
     </row>
     <row r="247">
@@ -7925,13 +7925,13 @@
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.001908858862261561</v>
+        <v>0.001908858862262429</v>
       </c>
       <c r="F247" t="n">
         <v>0.9960148852688991</v>
       </c>
       <c r="G247" t="n">
-        <v>0.002076255868837663</v>
+        <v>0.002076255868838135</v>
       </c>
     </row>
     <row r="248">
@@ -7948,13 +7948,13 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.002182151498772424</v>
+        <v>0.002182151498773913</v>
       </c>
       <c r="F248" t="n">
         <v>0.9578011292197038</v>
       </c>
       <c r="G248" t="n">
-        <v>0.04001671928151788</v>
+        <v>0.04001671928156337</v>
       </c>
     </row>
     <row r="249">
@@ -7971,13 +7971,13 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>0.001816256970758147</v>
+        <v>0.001816256970759799</v>
       </c>
       <c r="F249" t="n">
         <v>0.9267721842831552</v>
       </c>
       <c r="G249" t="n">
-        <v>0.07141155874603612</v>
+        <v>0.07141155874610107</v>
       </c>
     </row>
     <row r="250">
@@ -7994,13 +7994,13 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0.004172845354671403</v>
+        <v>0.004172845354675199</v>
       </c>
       <c r="F250" t="n">
         <v>0.9201282614959555</v>
       </c>
       <c r="G250" t="n">
-        <v>0.07569889314932993</v>
+        <v>0.07569889314939877</v>
       </c>
     </row>
     <row r="251">
@@ -8017,13 +8017,13 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>0.001253117902937025</v>
+        <v>0.001253117902937594</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8472583148098071</v>
+        <v>0.8472583148096144</v>
       </c>
       <c r="G251" t="n">
-        <v>0.1514885672872693</v>
+        <v>0.1514885672873727</v>
       </c>
     </row>
     <row r="252">
@@ -8040,13 +8040,13 @@
         <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0004049845920661126</v>
+        <v>0.0004049845920662968</v>
       </c>
       <c r="F252" t="n">
-        <v>0.8260427477234733</v>
+        <v>0.8260427477232855</v>
       </c>
       <c r="G252" t="n">
-        <v>0.1735522676844943</v>
+        <v>0.1735522676845732</v>
       </c>
     </row>
     <row r="253">
@@ -8057,19 +8057,19 @@
         <v>0.03445648173694641</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.007765814965729999</v>
+        <v>-0.00776581496573</v>
       </c>
       <c r="D253" t="n">
         <v>1</v>
       </c>
       <c r="E253" t="n">
-        <v>0.0002880229343096898</v>
+        <v>0.0002880229343097553</v>
       </c>
       <c r="F253" t="n">
-        <v>0.834431614334614</v>
+        <v>0.8344316143344243</v>
       </c>
       <c r="G253" t="n">
-        <v>0.1652803627310885</v>
+        <v>0.1652803627312012</v>
       </c>
     </row>
     <row r="254">
@@ -8086,13 +8086,13 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0.0004987929799344366</v>
+        <v>0.00049879297993455</v>
       </c>
       <c r="F254" t="n">
         <v>0.868288103435669</v>
       </c>
       <c r="G254" t="n">
-        <v>0.131213103584377</v>
+        <v>0.1312131035844665</v>
       </c>
     </row>
     <row r="255">
@@ -8109,13 +8109,13 @@
         <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0.001545200397893097</v>
+        <v>0.0015452003978938</v>
       </c>
       <c r="F255" t="n">
-        <v>0.9467122668968558</v>
+        <v>0.9467122668966406</v>
       </c>
       <c r="G255" t="n">
-        <v>0.05174253270531792</v>
+        <v>0.05174253270535322</v>
       </c>
     </row>
     <row r="256">
@@ -8132,13 +8132,13 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.003745915777114498</v>
+        <v>0.003745915777116202</v>
       </c>
       <c r="F256" t="n">
         <v>0.9962350361900797</v>
       </c>
       <c r="G256" t="n">
-        <v>1.904803282270884e-05</v>
+        <v>1.904803282272184e-05</v>
       </c>
     </row>
     <row r="257">
@@ -8155,13 +8155,13 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.008111717205452748</v>
+        <v>0.008111717205458282</v>
       </c>
       <c r="F257" t="n">
         <v>0.9918882818701706</v>
       </c>
       <c r="G257" t="n">
-        <v>9.24334369261752e-10</v>
+        <v>9.243343692619622e-10</v>
       </c>
     </row>
     <row r="258">
@@ -8178,13 +8178,13 @@
         <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0.01162804162992311</v>
+        <v>0.01162804162992839</v>
       </c>
       <c r="F258" t="n">
         <v>0.9869292197310324</v>
       </c>
       <c r="G258" t="n">
-        <v>0.001442738639105067</v>
+        <v>0.001442738639105723</v>
       </c>
     </row>
     <row r="259">
@@ -8201,13 +8201,13 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0.002863607741927514</v>
+        <v>0.002863607741928817</v>
       </c>
       <c r="F259" t="n">
         <v>0.9430512664988454</v>
       </c>
       <c r="G259" t="n">
-        <v>0.05408512575926363</v>
+        <v>0.05408512575928822</v>
       </c>
     </row>
     <row r="260">
@@ -8224,13 +8224,13 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0.0009799921496360185</v>
+        <v>0.0009799921496364641</v>
       </c>
       <c r="F260" t="n">
         <v>0.91831183739552</v>
       </c>
       <c r="G260" t="n">
-        <v>0.08070817045477044</v>
+        <v>0.08070817045484384</v>
       </c>
     </row>
     <row r="261">
@@ -8247,13 +8247,13 @@
         <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0.001289548938404404</v>
+        <v>0.001289548938404697</v>
       </c>
       <c r="F261" t="n">
-        <v>0.9176277714109177</v>
+        <v>0.9176277714107091</v>
       </c>
       <c r="G261" t="n">
-        <v>0.08108267965076654</v>
+        <v>0.0810826796508034</v>
       </c>
     </row>
     <row r="262">
@@ -8273,10 +8273,10 @@
         <v>0.002634118131692067</v>
       </c>
       <c r="F262" t="n">
-        <v>0.928251139846995</v>
+        <v>0.928251139846784</v>
       </c>
       <c r="G262" t="n">
-        <v>0.06911474202140963</v>
+        <v>0.06911474202142534</v>
       </c>
     </row>
     <row r="263">
@@ -8293,13 +8293,13 @@
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>0.00633325520834326</v>
+        <v>0.006333255208346139</v>
       </c>
       <c r="F263" t="n">
         <v>0.9186482060965636</v>
       </c>
       <c r="G263" t="n">
-        <v>0.07501853869500405</v>
+        <v>0.07501853869503818</v>
       </c>
     </row>
     <row r="264">
@@ -8316,13 +8316,13 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.0137646841267422</v>
+        <v>0.01376468412674533</v>
       </c>
       <c r="F264" t="n">
-        <v>0.8766121050072746</v>
+        <v>0.8766121050070752</v>
       </c>
       <c r="G264" t="n">
-        <v>0.1096232108660308</v>
+        <v>0.1096232108660806</v>
       </c>
     </row>
     <row r="265">
@@ -8339,13 +8339,13 @@
         <v>1</v>
       </c>
       <c r="E265" t="n">
-        <v>0.02362201269482135</v>
+        <v>0.02362201269483209</v>
       </c>
       <c r="F265" t="n">
         <v>0.8531203509034623</v>
       </c>
       <c r="G265" t="n">
-        <v>0.1232576364017424</v>
+        <v>0.1232576364017985</v>
       </c>
     </row>
     <row r="266">
@@ -8365,10 +8365,10 @@
         <v>0.007148389005442006</v>
       </c>
       <c r="F266" t="n">
-        <v>0.587580310268172</v>
+        <v>0.5875803102679048</v>
       </c>
       <c r="G266" t="n">
-        <v>0.4052713007264835</v>
+        <v>0.4052713007265757</v>
       </c>
     </row>
     <row r="267">
@@ -8385,13 +8385,13 @@
         <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.004179729593651138</v>
+        <v>0.004179729593653038</v>
       </c>
       <c r="F267" t="n">
-        <v>0.4279839557346524</v>
+        <v>0.4279839557345551</v>
       </c>
       <c r="G267" t="n">
-        <v>0.5678363146716052</v>
+        <v>0.5678363146718634</v>
       </c>
     </row>
     <row r="268">
@@ -8408,13 +8408,13 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.003047327332273859</v>
+        <v>0.003047327332274551</v>
       </c>
       <c r="F268" t="n">
-        <v>0.3558512619233037</v>
+        <v>0.3558512619230609</v>
       </c>
       <c r="G268" t="n">
-        <v>0.6411014107445002</v>
+        <v>0.641101410744646</v>
       </c>
     </row>
     <row r="269">
@@ -8431,13 +8431,13 @@
         <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.002349069659661064</v>
+        <v>0.00234906965966053</v>
       </c>
       <c r="F269" t="n">
-        <v>0.3280117270205248</v>
+        <v>0.328011727020301</v>
       </c>
       <c r="G269" t="n">
-        <v>0.6696392033198091</v>
+        <v>0.6696392033199613</v>
       </c>
     </row>
     <row r="270">
@@ -8457,10 +8457,10 @@
         <v>0.001117144538834369</v>
       </c>
       <c r="F270" t="n">
-        <v>0.3019838627252683</v>
+        <v>0.3019838627251311</v>
       </c>
       <c r="G270" t="n">
-        <v>0.6968989927359601</v>
+        <v>0.6968989927361185</v>
       </c>
     </row>
     <row r="271">
@@ -8477,13 +8477,13 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0.000457336155904976</v>
+        <v>0.0004573361559050799</v>
       </c>
       <c r="F271" t="n">
-        <v>0.2932989787073487</v>
+        <v>0.2932989787072154</v>
       </c>
       <c r="G271" t="n">
-        <v>0.7062436851367374</v>
+        <v>0.7062436851368979</v>
       </c>
     </row>
     <row r="272">
@@ -8503,10 +8503,10 @@
         <v>0.000380619963549985</v>
       </c>
       <c r="F272" t="n">
-        <v>0.3048292063959914</v>
+        <v>0.3048292063958528</v>
       </c>
       <c r="G272" t="n">
-        <v>0.6947901736405104</v>
+        <v>0.6947901736406684</v>
       </c>
     </row>
     <row r="273">
@@ -8523,13 +8523,13 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0.0008073412141110909</v>
+        <v>0.0008073412141109073</v>
       </c>
       <c r="F273" t="n">
-        <v>0.3472126057495796</v>
+        <v>0.3472126057494218</v>
       </c>
       <c r="G273" t="n">
-        <v>0.6519800530363462</v>
+        <v>0.6519800530364944</v>
       </c>
     </row>
     <row r="274">
@@ -8546,10 +8546,10 @@
         <v>1</v>
       </c>
       <c r="E274" t="n">
-        <v>0.002116848018170258</v>
+        <v>0.002116848018169777</v>
       </c>
       <c r="F274" t="n">
-        <v>0.4296565879592595</v>
+        <v>0.4296565879590641</v>
       </c>
       <c r="G274" t="n">
         <v>0.5682265640226768</v>
@@ -8598,7 +8598,7 @@
         <v>0.7212401672233669</v>
       </c>
       <c r="G276" t="n">
-        <v>0.2646241299405027</v>
+        <v>0.2646241299404425</v>
       </c>
     </row>
     <row r="277">
@@ -8615,13 +8615,13 @@
         <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0.03586742888831929</v>
+        <v>0.03586742888832745</v>
       </c>
       <c r="F277" t="n">
         <v>0.7722216674858678</v>
       </c>
       <c r="G277" t="n">
-        <v>0.1919109036257816</v>
+        <v>0.191910903625738</v>
       </c>
     </row>
     <row r="278">
@@ -8644,7 +8644,7 @@
         <v>0.7512067326637631</v>
       </c>
       <c r="G278" t="n">
-        <v>0.1256497185202621</v>
+        <v>0.125649718520205</v>
       </c>
     </row>
     <row r="279">
@@ -8661,13 +8661,13 @@
         <v>0</v>
       </c>
       <c r="E279" t="n">
-        <v>0.4561156464032811</v>
+        <v>0.4561156464034885</v>
       </c>
       <c r="F279" t="n">
         <v>0.4726897487306733</v>
       </c>
       <c r="G279" t="n">
-        <v>0.07119460486595647</v>
+        <v>0.07119460486594029</v>
       </c>
     </row>
     <row r="280">
@@ -8687,10 +8687,10 @@
         <v>0.5633493005545046</v>
       </c>
       <c r="F280" t="n">
-        <v>0.4206426742403847</v>
+        <v>0.4206426742401934</v>
       </c>
       <c r="G280" t="n">
-        <v>0.01600802520520369</v>
+        <v>0.01600802520519277</v>
       </c>
     </row>
     <row r="281">
@@ -8713,7 +8713,7 @@
         <v>0.1540633885101887</v>
       </c>
       <c r="G281" t="n">
-        <v>0.001046201620597662</v>
+        <v>0.001046201620597424</v>
       </c>
     </row>
     <row r="282">
@@ -8736,7 +8736,7 @@
         <v>0.004097778303611798</v>
       </c>
       <c r="G282" t="n">
-        <v>0.0006238607223014426</v>
+        <v>0.0006238607223013006</v>
       </c>
     </row>
     <row r="283">
@@ -8756,7 +8756,7 @@
         <v>0.9953758895608776</v>
       </c>
       <c r="F283" t="n">
-        <v>0.004155010397387285</v>
+        <v>0.00415501039738634</v>
       </c>
       <c r="G283" t="n">
         <v>0.0004691000416374085</v>
@@ -8779,10 +8779,10 @@
         <v>0.9982147487103938</v>
       </c>
       <c r="F284" t="n">
-        <v>0.001779666314833477</v>
+        <v>0.001779666314833882</v>
       </c>
       <c r="G284" t="n">
-        <v>5.584974744685282e-06</v>
+        <v>5.584974744682741e-06</v>
       </c>
     </row>
     <row r="285">
@@ -8802,10 +8802,10 @@
         <v>0.99956675344574</v>
       </c>
       <c r="F285" t="n">
-        <v>0.0004252291512010046</v>
+        <v>0.0004252291512009079</v>
       </c>
       <c r="G285" t="n">
-        <v>8.017403006772374e-06</v>
+        <v>8.017403006768729e-06</v>
       </c>
     </row>
     <row r="286">
@@ -8825,10 +8825,10 @@
         <v>0.999954144523163</v>
       </c>
       <c r="F286" t="n">
-        <v>2.410976739958854e-05</v>
+        <v>2.410976739957209e-05</v>
       </c>
       <c r="G286" t="n">
-        <v>2.174570954974517e-05</v>
+        <v>2.174570954973034e-05</v>
       </c>
     </row>
     <row r="287">
@@ -8848,10 +8848,10 @@
         <v>0.9999235771804101</v>
       </c>
       <c r="F287" t="n">
-        <v>1.763605242275594e-06</v>
+        <v>1.763605242272386e-06</v>
       </c>
       <c r="G287" t="n">
-        <v>7.465921439111495e-05</v>
+        <v>7.4659214391081e-05</v>
       </c>
     </row>
     <row r="288">
@@ -8871,10 +8871,10 @@
         <v>0.9558072515424849</v>
       </c>
       <c r="F288" t="n">
-        <v>0.001056134669476916</v>
+        <v>0.001056134669472834</v>
       </c>
       <c r="G288" t="n">
-        <v>0.04313661378797811</v>
+        <v>0.04313661378795849</v>
       </c>
     </row>
     <row r="289">
@@ -8894,10 +8894,10 @@
         <v>0.8767192470738215</v>
       </c>
       <c r="F289" t="n">
-        <v>0.001249111438812016</v>
+        <v>0.001249111438808608</v>
       </c>
       <c r="G289" t="n">
-        <v>0.1220316414874743</v>
+        <v>0.1220316414874188</v>
       </c>
     </row>
     <row r="290">
@@ -8917,10 +8917,10 @@
         <v>0.8226761196387538</v>
       </c>
       <c r="F290" t="n">
-        <v>0.002744955773829877</v>
+        <v>0.00274495577382738</v>
       </c>
       <c r="G290" t="n">
-        <v>0.1745789245874676</v>
+        <v>0.1745789245874279</v>
       </c>
     </row>
     <row r="291">
@@ -8937,13 +8937,13 @@
         <v>2</v>
       </c>
       <c r="E291" t="n">
-        <v>0.5310793468219048</v>
+        <v>0.5310793468220256</v>
       </c>
       <c r="F291" t="n">
-        <v>0.001672265724350843</v>
+        <v>0.001672265724349702</v>
       </c>
       <c r="G291" t="n">
-        <v>0.467248387453797</v>
+        <v>0.4672483874536908</v>
       </c>
     </row>
     <row r="292">
@@ -8960,10 +8960,10 @@
         <v>2</v>
       </c>
       <c r="E292" t="n">
-        <v>0.3524176379596244</v>
+        <v>0.3524176379597045</v>
       </c>
       <c r="F292" t="n">
-        <v>0.001095633379435821</v>
+        <v>0.001095633379435322</v>
       </c>
       <c r="G292" t="n">
         <v>0.6464867286609397</v>
@@ -8983,10 +8983,10 @@
         <v>2</v>
       </c>
       <c r="E293" t="n">
-        <v>0.1416626393548275</v>
+        <v>0.1416626393548597</v>
       </c>
       <c r="F293" t="n">
-        <v>0.003182816884807938</v>
+        <v>0.003182816884808662</v>
       </c>
       <c r="G293" t="n">
         <v>0.8551545437604114</v>
@@ -9006,10 +9006,10 @@
         <v>2</v>
       </c>
       <c r="E294" t="n">
-        <v>0.0273766924597061</v>
+        <v>0.02737669245971232</v>
       </c>
       <c r="F294" t="n">
-        <v>0.005828032298494424</v>
+        <v>0.005828032298497074</v>
       </c>
       <c r="G294" t="n">
         <v>0.9667952752417144</v>
@@ -9029,10 +9029,10 @@
         <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>0.0102914147527665</v>
+        <v>0.01029141475276884</v>
       </c>
       <c r="F295" t="n">
-        <v>0.008889341764608422</v>
+        <v>0.008889341764612464</v>
       </c>
       <c r="G295" t="n">
         <v>0.9808192434825813</v>
@@ -9052,10 +9052,10 @@
         <v>2</v>
       </c>
       <c r="E296" t="n">
-        <v>0.006845259467375893</v>
+        <v>0.006845259467379006</v>
       </c>
       <c r="F296" t="n">
-        <v>0.01901442983194284</v>
+        <v>0.01901442983196446</v>
       </c>
       <c r="G296" t="n">
         <v>0.9741403107007688</v>
@@ -9075,10 +9075,10 @@
         <v>2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.005010772827274669</v>
+        <v>0.005010772827276948</v>
       </c>
       <c r="F297" t="n">
-        <v>0.01510753802247528</v>
+        <v>0.01510753802248902</v>
       </c>
       <c r="G297" t="n">
         <v>0.9798816891502107</v>
@@ -9098,10 +9098,10 @@
         <v>2</v>
       </c>
       <c r="E298" t="n">
-        <v>0.006776213342660598</v>
+        <v>0.006776213342665221</v>
       </c>
       <c r="F298" t="n">
-        <v>0.01208418181045694</v>
+        <v>0.01208418181046518</v>
       </c>
       <c r="G298" t="n">
         <v>0.9811396048468417</v>
@@ -9121,10 +9121,10 @@
         <v>2</v>
       </c>
       <c r="E299" t="n">
-        <v>0.01208285630943404</v>
+        <v>0.01208285630944502</v>
       </c>
       <c r="F299" t="n">
-        <v>0.004003039301534635</v>
+        <v>0.004003039301538275</v>
       </c>
       <c r="G299" t="n">
         <v>0.9839141043890737</v>
@@ -9144,13 +9144,13 @@
         <v>2</v>
       </c>
       <c r="E300" t="n">
-        <v>0.01068346119257232</v>
+        <v>0.01068346119257961</v>
       </c>
       <c r="F300" t="n">
-        <v>0.003491186942905883</v>
+        <v>0.003491186942908265</v>
       </c>
       <c r="G300" t="n">
-        <v>0.9858253518646318</v>
+        <v>0.9858253518644077</v>
       </c>
     </row>
     <row r="301">
@@ -9167,10 +9167,10 @@
         <v>2</v>
       </c>
       <c r="E301" t="n">
-        <v>0.01017648664835085</v>
+        <v>0.01017648664836011</v>
       </c>
       <c r="F301" t="n">
-        <v>0.003699292582460584</v>
+        <v>0.003699292582463108</v>
       </c>
       <c r="G301" t="n">
         <v>0.9861242207692612</v>
@@ -9190,10 +9190,10 @@
         <v>2</v>
       </c>
       <c r="E302" t="n">
-        <v>0.004914504984286566</v>
+        <v>0.004914504984291036</v>
       </c>
       <c r="F302" t="n">
-        <v>0.004705822171588745</v>
+        <v>0.004705822171593026</v>
       </c>
       <c r="G302" t="n">
         <v>0.9903796728440353</v>
@@ -9207,16 +9207,16 @@
         <v>0.01197547558860675</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.006295415534405311</v>
+        <v>-0.00629541553440531</v>
       </c>
       <c r="D303" t="n">
         <v>2</v>
       </c>
       <c r="E303" t="n">
-        <v>0.001148560878963122</v>
+        <v>0.001148560878964167</v>
       </c>
       <c r="F303" t="n">
-        <v>0.006613293925607151</v>
+        <v>0.006613293925611662</v>
       </c>
       <c r="G303" t="n">
         <v>0.9922381451954355</v>
@@ -9236,10 +9236,10 @@
         <v>2</v>
       </c>
       <c r="E304" t="n">
-        <v>0.0006938061580884744</v>
+        <v>0.0006938061580892632</v>
       </c>
       <c r="F304" t="n">
-        <v>0.01029246236444955</v>
+        <v>0.01029246236445423</v>
       </c>
       <c r="G304" t="n">
         <v>0.9890137314774337</v>
@@ -9259,10 +9259,10 @@
         <v>2</v>
       </c>
       <c r="E305" t="n">
-        <v>0.0004653989991913995</v>
+        <v>0.0004653989991919286</v>
       </c>
       <c r="F305" t="n">
-        <v>0.007119642169198317</v>
+        <v>0.007119642169204792</v>
       </c>
       <c r="G305" t="n">
         <v>0.9924149588316123</v>
@@ -9282,10 +9282,10 @@
         <v>2</v>
       </c>
       <c r="E306" t="n">
-        <v>0.001103925549696372</v>
+        <v>0.001103925549697627</v>
       </c>
       <c r="F306" t="n">
-        <v>0.003863763654218098</v>
+        <v>0.003863763654221611</v>
       </c>
       <c r="G306" t="n">
         <v>0.9950323107961441</v>
@@ -9305,10 +9305,10 @@
         <v>2</v>
       </c>
       <c r="E307" t="n">
-        <v>0.0002594961285629001</v>
+        <v>0.0002594961285631951</v>
       </c>
       <c r="F307" t="n">
-        <v>0.006037484012598635</v>
+        <v>0.006037484012602753</v>
       </c>
       <c r="G307" t="n">
         <v>0.9937030198589409</v>
@@ -9328,10 +9328,10 @@
         <v>2</v>
       </c>
       <c r="E308" t="n">
-        <v>7.252876725030822e-05</v>
+        <v>7.252876725037419e-05</v>
       </c>
       <c r="F308" t="n">
-        <v>0.008058622408755956</v>
+        <v>0.008058622408761451</v>
       </c>
       <c r="G308" t="n">
         <v>0.991868848823897</v>
@@ -9351,10 +9351,10 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>7.361919821408229e-05</v>
+        <v>7.361919821414925e-05</v>
       </c>
       <c r="F309" t="n">
-        <v>0.01110166018608918</v>
+        <v>0.01110166018609676</v>
       </c>
       <c r="G309" t="n">
         <v>0.9888247206157867</v>
@@ -9374,13 +9374,13 @@
         <v>2</v>
       </c>
       <c r="E310" t="n">
-        <v>5.551658718347218e-05</v>
+        <v>5.551658718349743e-05</v>
       </c>
       <c r="F310" t="n">
-        <v>0.01041428480752124</v>
+        <v>0.01041428480752598</v>
       </c>
       <c r="G310" t="n">
-        <v>0.9895301986052358</v>
+        <v>0.9895301986052357</v>
       </c>
     </row>
     <row r="311">
@@ -9397,10 +9397,10 @@
         <v>2</v>
       </c>
       <c r="E311" t="n">
-        <v>7.673194373814579e-05</v>
+        <v>7.673194373821557e-05</v>
       </c>
       <c r="F311" t="n">
-        <v>0.01098766870722248</v>
+        <v>0.01098766870722748</v>
       </c>
       <c r="G311" t="n">
         <v>0.9889355993490704</v>
@@ -9420,10 +9420,10 @@
         <v>2</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0002461774391574559</v>
+        <v>0.0002461774391576238</v>
       </c>
       <c r="F312" t="n">
-        <v>0.01256545998216478</v>
+        <v>0.01256545998217049</v>
       </c>
       <c r="G312" t="n">
         <v>0.987188362578618</v>
@@ -9443,10 +9443,10 @@
         <v>2</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0001164349922357097</v>
+        <v>0.0001164349922358156</v>
       </c>
       <c r="F313" t="n">
-        <v>0.03895494486633589</v>
+        <v>0.03895494486635361</v>
       </c>
       <c r="G313" t="n">
         <v>0.9609286201413866</v>
@@ -9466,10 +9466,10 @@
         <v>2</v>
       </c>
       <c r="E314" t="n">
-        <v>0.000205942217525129</v>
+        <v>0.0002059422175252695</v>
       </c>
       <c r="F314" t="n">
-        <v>0.06992470205799518</v>
+        <v>0.06992470205804288</v>
       </c>
       <c r="G314" t="n">
         <v>0.9298693557245332</v>
@@ -9489,10 +9489,10 @@
         <v>2</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0001693233777021225</v>
+        <v>0.000169323377702238</v>
       </c>
       <c r="F315" t="n">
-        <v>0.1730601723648291</v>
+        <v>0.1730601723649078</v>
       </c>
       <c r="G315" t="n">
         <v>0.8267705042574903</v>
@@ -9512,13 +9512,13 @@
         <v>2</v>
       </c>
       <c r="E316" t="n">
-        <v>0.0006845457928813858</v>
+        <v>0.0006845457928820085</v>
       </c>
       <c r="F316" t="n">
-        <v>0.3717310848383265</v>
+        <v>0.37173108483858</v>
       </c>
       <c r="G316" t="n">
-        <v>0.6275843693688952</v>
+        <v>0.6275843693684671</v>
       </c>
     </row>
     <row r="317">
@@ -9529,19 +9529,19 @@
         <v>-0.06138811628823403</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0003471971954322061</v>
+        <v>0.0003471971954322065</v>
       </c>
       <c r="D317" t="n">
         <v>2</v>
       </c>
       <c r="E317" t="n">
-        <v>0.003524528532568573</v>
+        <v>0.003524528532570977</v>
       </c>
       <c r="F317" t="n">
-        <v>0.4337065478312357</v>
+        <v>0.4337065478315316</v>
       </c>
       <c r="G317" t="n">
-        <v>0.5627689236362202</v>
+        <v>0.5627689236359643</v>
       </c>
     </row>
     <row r="318">
@@ -9558,13 +9558,13 @@
         <v>2</v>
       </c>
       <c r="E318" t="n">
-        <v>0.00274920378776258</v>
+        <v>0.002749203787764455</v>
       </c>
       <c r="F318" t="n">
-        <v>0.3591958817419164</v>
+        <v>0.3591958817420797</v>
       </c>
       <c r="G318" t="n">
-        <v>0.6380549144704136</v>
+        <v>0.6380549144701235</v>
       </c>
     </row>
     <row r="319">
@@ -9581,13 +9581,13 @@
         <v>2</v>
       </c>
       <c r="E319" t="n">
-        <v>0.003577535690586642</v>
+        <v>0.003577535690589083</v>
       </c>
       <c r="F319" t="n">
-        <v>0.2862614407768519</v>
+        <v>0.2862614407769821</v>
       </c>
       <c r="G319" t="n">
-        <v>0.7101610235326156</v>
+        <v>0.710161023532454</v>
       </c>
     </row>
     <row r="320">
@@ -9604,13 +9604,13 @@
         <v>2</v>
       </c>
       <c r="E320" t="n">
-        <v>0.00229748078511641</v>
+        <v>0.002297480785117456</v>
       </c>
       <c r="F320" t="n">
-        <v>0.165322690295358</v>
+        <v>0.1653226902954331</v>
       </c>
       <c r="G320" t="n">
-        <v>0.8323798289195553</v>
+        <v>0.832379828919366</v>
       </c>
     </row>
     <row r="321">
@@ -9627,10 +9627,10 @@
         <v>2</v>
       </c>
       <c r="E321" t="n">
-        <v>0.0009469689101599169</v>
+        <v>0.0009469689101603476</v>
       </c>
       <c r="F321" t="n">
-        <v>0.09511722969386067</v>
+        <v>0.09511722969390393</v>
       </c>
       <c r="G321" t="n">
         <v>0.9039358013959043</v>
@@ -9650,10 +9650,10 @@
         <v>2</v>
       </c>
       <c r="E322" t="n">
-        <v>0.0004948326297494585</v>
+        <v>0.000494832629749796</v>
       </c>
       <c r="F322" t="n">
-        <v>0.06488221546973943</v>
+        <v>0.06488221546975419</v>
       </c>
       <c r="G322" t="n">
         <v>0.9346229519004927</v>
@@ -9673,7 +9673,7 @@
         <v>2</v>
       </c>
       <c r="E323" t="n">
-        <v>0.0002529914074970945</v>
+        <v>0.0002529914074972096</v>
       </c>
       <c r="F323" t="n">
         <v>0.04788007537738995</v>
@@ -9696,10 +9696,10 @@
         <v>2</v>
       </c>
       <c r="E324" t="n">
-        <v>0.0001428442025964235</v>
+        <v>0.0001428442025964885</v>
       </c>
       <c r="F324" t="n">
-        <v>0.04126191965846758</v>
+        <v>0.04126191965847696</v>
       </c>
       <c r="G324" t="n">
         <v>0.9585952361388326</v>
@@ -9719,10 +9719,10 @@
         <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0001299301313773977</v>
+        <v>0.0001299301313774864</v>
       </c>
       <c r="F325" t="n">
-        <v>0.04336978771565508</v>
+        <v>0.04336978771566494</v>
       </c>
       <c r="G325" t="n">
         <v>0.956500282152918</v>
@@ -9733,7 +9733,7 @@
         <v>46022</v>
       </c>
       <c r="B326" t="n">
-        <v>-0.002782332919957095</v>
+        <v>-0.002782332919957094</v>
       </c>
       <c r="C326" t="n">
         <v>-0.009222956945157942</v>
@@ -9742,10 +9742,10 @@
         <v>2</v>
       </c>
       <c r="E326" t="n">
-        <v>0.0001730661188763901</v>
+        <v>0.0001730661188765475</v>
       </c>
       <c r="F326" t="n">
-        <v>0.0473233991748724</v>
+        <v>0.04732339917488317</v>
       </c>
       <c r="G326" t="n">
         <v>0.9525035347063255</v>
@@ -9765,10 +9765,10 @@
         <v>2</v>
       </c>
       <c r="E327" t="n">
-        <v>0.0003535184168985279</v>
+        <v>0.0003535184168988495</v>
       </c>
       <c r="F327" t="n">
-        <v>0.06500861623091458</v>
+        <v>0.06500861623092936</v>
       </c>
       <c r="G327" t="n">
         <v>0.9346378653522509</v>
